--- a/apps/api/src/assets/content/Jetstream - Load Records to Multiple Objects - Template.xlsx
+++ b/apps/api/src/assets/content/Jetstream - Load Records to Multiple Objects - Template.xlsx
@@ -10,41 +10,25 @@
   <definedNames/>
   <calcPr/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataSignature="AMtx7mhOpWATYGE1TOUyx8V5Ct6NpR94fw=="/>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="PpWgn1j/ff8QGThW1Nau+lNR4eASApl2TECYnR2WXbQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="E43">
+    <comment authorId="0" ref="F6">
       <text>
         <t xml:space="preserve">======
-ID#AAAANdv2em4
-Jetstream Support    (2021-07-16 22:30:36)
-The "Reference Id" column can have any name you want as long as it is different from any other field headers in the dataset.</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="E32">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAANdv2em0
-Jetstream Support    (2021-07-16 22:30:28)
-The "Reference Id" column can have any name you want as long as it is different from any other field headers in the dataset.</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="H44">
-      <text>
-        <t xml:space="preserve">======
-ID#AAAANACe9Is
-Jetstream Support    (2021-07-12 03:14:52)
-If you are exporting records from Org 1, use the Record Id as the Reference Id to make it really easy to load the data and link the records together.</t>
+ID#AAAANACe9Hg
+Jetstream Support    (2021-07-12 03:06:57)
+Valid values are: Insert, Update or Upsert</t>
       </text>
     </comment>
     <comment authorId="0" ref="E33">
@@ -55,12 +39,22 @@
 If you are exporting records from Org 1, use the Record Id as the Reference Id to make it really easy to load the data and link the records together.</t>
       </text>
     </comment>
-    <comment authorId="0" ref="N22">
+    <comment authorId="0" ref="H20">
       <text>
         <t xml:space="preserve">======
-ID#AAAANACe9Ig
-Jetstream Support    (2021-07-12 03:13:31)
-This value will be hard-coded to the provided id, while the other two records will be associated to accounts that are inserted as part of the data load.</t>
+ID#AAAANACe9H4
+Jetstream Support    (2021-07-12 03:11:09)
+Adding curly brackets around a field heading tells Jetstream that the values for this field are Reference Ids to other records in the load.
+In this example, the AccountId lookup field will be populated with the Id's of the accounts on the "Accounts" worksheet with matching Reference Id's.
+These records will be added to a group of records when loading into Salesforce.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="E32">
+      <text>
+        <t xml:space="preserve">======
+ID#AAAANdv2em0
+Jetstream Support    (2021-07-16 22:30:28)
+The "Reference Id" column can have any name you want as long as it is different from any other field headers in the dataset.</t>
       </text>
     </comment>
     <comment authorId="0" ref="N23">
@@ -73,6 +67,14 @@
 This record will be added to a group of records when loading into Salesforce.</t>
       </text>
     </comment>
+    <comment authorId="0" ref="N22">
+      <text>
+        <t xml:space="preserve">======
+ID#AAAANACe9Ig
+Jetstream Support    (2021-07-12 03:13:31)
+This value will be hard-coded to the provided id, while the other two records will be associated to accounts that are inserted as part of the data load.</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="N21">
       <text>
         <t xml:space="preserve">======
@@ -83,14 +85,20 @@
 This record will be added to a group of records when loading into Salesforce.</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H20">
+    <comment authorId="0" ref="E43">
       <text>
         <t xml:space="preserve">======
-ID#AAAANACe9H4
-Jetstream Support    (2021-07-12 03:11:09)
-Adding curly brackets around a field heading tells Jetstream that the values for this field are Reference Id's to other records in the load.
-In this example, the AccountId lookup field will be populated with the Id's of the accounts on the "Accounts" worksheet with matching Reference Id's.
-These records will be added to a group of records when loading into Salesforce.</t>
+ID#AAAANdv2em4
+Jetstream Support    (2021-07-16 22:30:36)
+The "Reference Id" column can have any name you want as long as it is different from any other field headers in the dataset.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="H44">
+      <text>
+        <t xml:space="preserve">======
+ID#AAAANACe9Is
+Jetstream Support    (2021-07-12 03:14:52)
+If you are exporting records from Org 1, use the Record Id as the Reference Id to make it really easy to load the data and link the records together.</t>
       </text>
     </comment>
     <comment authorId="0" ref="G9">
@@ -98,210 +106,304 @@
         <t xml:space="preserve">======
 ID#AAAANACe9Hw
 Jetstream Support    (2021-07-12 03:10:15)
-Adding curly brackets around a field heading tells Jetstream that the values for this field are Reference Id's to other records in the load.
+Adding curly brackets around a field heading tells Jetstream that the values for this field are Reference Ids to other records in the load.
 In this example, the ParentId lookup field will be populated with the Id of row 6 ("account1").
 These records will be added to a group of records when loading into Salesforce.</t>
       </text>
     </comment>
-    <comment authorId="0" ref="F6">
+  </commentList>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mgFiJhIFIEYxCqUdojPxuzTSxEQlg=="/>
+    </ext>
+  </extLst>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="A5">
       <text>
         <t xml:space="preserve">======
-ID#AAAANACe9Hg
-Jetstream Support    (2021-07-12 03:06:57)
-Valid values are: Insert, Update or Upsert</t>
+ID#AAACFdEhe0w
+Jetstream Support    (2026-08-11 02:18:30)
+The "Reference Id" column can have any unique name, as long as it is different from every other column header in the file.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="C5">
+      <text>
+        <t xml:space="preserve">======
+ID#AAACFdEhe00
+Jetstream Support    (2026-08-11 02:18:59)
+Adding curly braces around a field heading tells Jetstream that the values for this field are Reference Ids of other records in the load. Linked records form a group that loads as one all-or-nothing transaction (max 500 records and 15 objects per group).</t>
       </text>
     </comment>
   </commentList>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhJWRg9/VRFD0BTrv7mj+UKPVZXyA=="/>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mjhYzPFaw2QP7FwRW/oeDc54U4zZQ=="/>
+    </ext>
+  </extLst>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="A5">
+      <text>
+        <t xml:space="preserve">======
+ID#AAACFdEhe0s
+Jetstream Support    (2026-08-11 02:18:16)
+The "Reference Id" column can have any unique name, as long as it is different from every other column header in the file.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="D5">
+      <text>
+        <t xml:space="preserve">======
+ID#AAACFdEhe04
+Jetstream Support    (2026-08-11 02:19:06)
+Adding curly braces around a field heading tells Jetstream that the values for this field are Reference Ids of other records in the load. Linked records form a group that loads as one all-or-nothing transaction (max 500 records and 15 objects per group).</t>
+      </text>
+    </comment>
+  </commentList>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mgavros7/KElV+z9bv9uGKyWVcvow=="/>
     </ext>
   </extLst>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="64">
-  <si>
-    <t>Load to Multiple Objects Instructions and Template</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="82">
+  <si>
+    <t>Object Api Name</t>
+  </si>
+  <si>
+    <t>Load to Multiple Objects — Instructions and Template</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>Insert</t>
+  </si>
+  <si>
+    <t>External Id (for upsert)</t>
+  </si>
+  <si>
+    <t>EXAMPLE</t>
+  </si>
+  <si>
+    <t>Reference Id</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>{ParentId}</t>
+  </si>
+  <si>
+    <t>{AccountId}</t>
+  </si>
+  <si>
+    <t>Every worksheet in this file is loaded unless its name contains "instructions". That includes the example worksheets "Create Accounts" and "Create Contacts".  Replace their contents with your own data before loading.</t>
+  </si>
+  <si>
+    <t>WORKSHEET: Accounts</t>
+  </si>
+  <si>
+    <t>contact1</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>account1</t>
+  </si>
+  <si>
+    <t>Account 1</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>contact2</t>
+  </si>
+  <si>
+    <t>Janet</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>account2</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Account 2</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>contact3</t>
+  </si>
+  <si>
+    <t>account3</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>Account 3</t>
+  </si>
+  <si>
+    <t>Jackson</t>
+  </si>
+  <si>
+    <t>Quick start</t>
   </si>
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <i/>
+        <rFont val="Arial"/>
+        <b/>
         <color theme="1"/>
-        <sz val="12.0"/>
       </rPr>
-      <t xml:space="preserve">This template can be used to load files - any worksheet named "Instructions" will not be processed
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Create one worksheet for each object and operation you want to perform. Use the example worksheets as a starting point and replace their contents with your data.
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
+        <b/>
         <color theme="1"/>
-        <sz val="12.0"/>
       </rPr>
-      <t xml:space="preserve">1. Create a worksheet for each operation that you would like to perform. Use the example worksheets in this template as a starting point.
-2. Populate the </t>
+      <t xml:space="preserve">2. </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <b/>
+        <rFont val="Arial"/>
         <color theme="1"/>
-        <sz val="12.0"/>
       </rPr>
-      <t>Object API Name</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>Operation</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t xml:space="preserve">. If you are performing an Upsert, then provide the External Id field API Name as well. This field must also exist in your data set.
-3. Put all your records with the field API names as the column headers starting in cell B5.
-4. Populate the "Reference Id" in column A for each record. If you are moving records from Org 1 to Org 2, you can use the record Id from Org 1 as the Reference Id.
+      <t xml:space="preserve">In each worksheet, enter the Object API Name in cell B1 and the Operation (Insert, Update, or Upsert) in cell B2. For Upsert, enter the External Id field API name in cell B3 — that field must also be included as a column in your data.
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
-        <i/>
+        <rFont val="Arial"/>
+        <b/>
         <color theme="1"/>
-        <sz val="12.0"/>
       </rPr>
-      <t>The Reference Id must be unique across all records in the spreadhseet and is used to link related records together.</t>
+      <t xml:space="preserve">3. </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <color theme="1"/>
-        <sz val="12.0"/>
       </rPr>
-      <t xml:space="preserve">
-5. To link a record with another record in the data load, you can indicate this in the header or the row using one of the following:
-5a. The easiest approach is to indicate at the header level that each row will have a related Reference Id to another record in the dataset, or it can be blank for some rows. Wrap the heading in curley braces e.x. {AccountId}
-5b. If you need to specify some hard-coded values for some rows, but other rows need to relate to a Reference Id from another record in the dataset, wrap the value in the row in curley braces. e.x. {account1}
-6. Once you load your file, it will be validated to ensure that everything is valid and filled out correctly.
-7. Your data is split into groups based on how the data is related to each other. All records within a group will either all succeed or all fail, each group of related records will never be left in a partial state.
+      <t xml:space="preserve">Put your column headers on row 5. Cell A5 is the Reference Id column header — give it any unique name. The remaining headers are field API names.
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <b/>
         <color theme="1"/>
-        <sz val="12.0"/>
       </rPr>
-      <t>Considerations</t>
+      <t xml:space="preserve">4. </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <color theme="1"/>
-        <sz val="12.0"/>
       </rPr>
-      <t xml:space="preserve">:
+      <t xml:space="preserve">Enter one record per row starting on row 6, and give every record a unique Reference Id in column A.
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <b/>
         <color theme="1"/>
-        <sz val="12.0"/>
       </rPr>
-      <t xml:space="preserve">- </t>
+      <t xml:space="preserve">5. </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Calibri"/>
+        <rFont val="Arial"/>
         <color theme="1"/>
-        <sz val="12.0"/>
       </rPr>
-      <t xml:space="preserve">You cannot have more than 500 records that are related to each other.
-- You can load to no more than 15 different objects.
+      <t xml:space="preserve">Link related records together using curly braces — see "Linking records" below.
 </t>
     </r>
-  </si>
-  <si>
-    <t>EXAMPLE</t>
-  </si>
-  <si>
-    <t>WORKSHEET: Accounts</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Object Api Name</t>
-  </si>
-  <si>
-    <t>Account</t>
-  </si>
-  <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>Insert</t>
-  </si>
-  <si>
-    <t>External Id (for upsert)</t>
-  </si>
-  <si>
-    <t>Reference Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>{ParentId}</t>
-  </si>
-  <si>
-    <t>account1</t>
-  </si>
-  <si>
-    <t>Account 1</t>
-  </si>
-  <si>
-    <t>account2</t>
-  </si>
-  <si>
-    <t>Account 2</t>
-  </si>
-  <si>
-    <t>account3</t>
-  </si>
-  <si>
-    <t>Account 3</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">6. </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Upload the file on the Load Records to Multiple Objects page. Jetstream validates the file and shows a preview of every worksheet and the computed groups before anything is loaded.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">7. </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>Start the load and review the per-record results for each worksheet. Failed groups can be retried, and results can be downloaded.</t>
+    </r>
   </si>
   <si>
     <t>WORKSHEET: Contacts</t>
@@ -310,49 +412,13 @@
     <t>Alternative approach to associate some rows to reference ids and hardcode a value in other rows</t>
   </si>
   <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>LastName</t>
-  </si>
-  <si>
-    <t>{AccountId}</t>
-  </si>
-  <si>
     <t>AccountId</t>
   </si>
   <si>
-    <t>contact1</t>
-  </si>
-  <si>
-    <t>Bob</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
     <t>{account1}</t>
   </si>
   <si>
-    <t>contact2</t>
-  </si>
-  <si>
-    <t>Janet</t>
-  </si>
-  <si>
     <t>0012J00002S20zqQAB</t>
-  </si>
-  <si>
-    <t>contact3</t>
-  </si>
-  <si>
-    <t>Alan</t>
-  </si>
-  <si>
-    <t>Jackson</t>
   </si>
   <si>
     <t>{account2}</t>
@@ -362,6 +428,36 @@
 Use the Ids from Org 1 as the Reference Id to easily load the records with their relationships</t>
   </si>
   <si>
+    <t>Reference Ids</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Must be unique across all worksheets in the file.
+May contain letters, numbers, and underscores, and must start with a letter or number.
+Only used during the load to link records together, not saved to Salesforce.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>Tip</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t>: when migrating records from one org to another, use each record's Id from the source org as its Reference Id. Lookup columns exported from the source org will then already contain valid Reference Ids.</t>
+    </r>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -383,6 +479,13 @@
     <t>Burlington Textiles Corp of America</t>
   </si>
   <si>
+    <t>How records are grouped</t>
+  </si>
+  <si>
+    <t>Rows that link to each other by Reference Id — directly or through other rows — form a group. Each group is sent to Salesforce as a single all-or-nothing transaction: if any record in the group fails, every record in the group is rolled back, so related records are never left in a partial state. Groups that are not linked to each other load independently.
+Example: contact1 and contact2 both link to account1, so account1 + contact1 + contact2 form ONE group of 3 records. contact3 links to account2, so account2 + contact3 form a separate group of 2 records. Five rows, two groups.</t>
+  </si>
+  <si>
     <t>0035000003G6jYfAAJ</t>
   </si>
   <si>
@@ -390,6 +493,59 @@
   </si>
   <si>
     <t>Pavlova</t>
+  </si>
+  <si>
+    <t>0035000003G6jYgAAJ</t>
+  </si>
+  <si>
+    <t>Jane</t>
+  </si>
+  <si>
+    <t>Grey</t>
+  </si>
+  <si>
+    <t>0035000003G6jYhAAJ</t>
+  </si>
+  <si>
+    <t>Ashley</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>0035000003G6jYiAAJ</t>
+  </si>
+  <si>
+    <t>Arthur</t>
+  </si>
+  <si>
+    <t>Song</t>
+  </si>
+  <si>
+    <t>Limits</t>
+  </si>
+  <si>
+    <t>0035000003G6jYjAAJ</t>
+  </si>
+  <si>
+    <t>Lauren</t>
+  </si>
+  <si>
+    <t>Boyle</t>
+  </si>
+  <si>
+    <t>Maximum 500 records per group of RELATED records. This is not a per-worksheet or per-file limit, only records linked to each other count toward it. For example, a 5,000-row file whose rows form groups of 5 loads fine.
+Maximum 15 different objects per group.
+No overall file limit, Jetstream automatically batches unrelated groups into multiple API calls.</t>
+  </si>
+  <si>
+    <t>WORKSHEET: Update Accounts</t>
+  </si>
+  <si>
+    <t>For Update, include an Id column so Salesforce knows which records to update.</t>
+  </si>
+  <si>
+    <t>Update</t>
   </si>
   <si>
     <r>
@@ -431,51 +587,40 @@
     </r>
   </si>
   <si>
-    <t>0035000003G6jYgAAJ</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>Grey</t>
-  </si>
-  <si>
-    <t>0035000003G6jYhAAJ</t>
-  </si>
-  <si>
-    <t>Ashley</t>
-  </si>
-  <si>
-    <t>James</t>
-  </si>
-  <si>
-    <t>0035000003G6jYiAAJ</t>
-  </si>
-  <si>
-    <t>Arthur</t>
-  </si>
-  <si>
-    <t>Song</t>
-  </si>
-  <si>
-    <t>0035000003G6jYjAAJ</t>
-  </si>
-  <si>
-    <t>Lauren</t>
-  </si>
-  <si>
-    <t>Boyle</t>
+    <t>WORKSHEET: Upsert Accounts</t>
+  </si>
+  <si>
+    <t>For Upsert, the External Id field in B3 must also appear as a data column.</t>
+  </si>
+  <si>
+    <t>Upsert</t>
+  </si>
+  <si>
+    <t>My_External_Id__c</t>
+  </si>
+  <si>
+    <t>ACCT-001</t>
+  </si>
+  <si>
+    <t>ACCT-002</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -484,6 +629,7 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -495,14 +641,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font/>
-    <font>
-      <b/>
-      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -511,23 +649,33 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="11.0"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font/>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="12.0"/>
       <color theme="1"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color rgb="FF000000"/>
-      <name val="Docs-Calibri"/>
     </font>
   </fonts>
   <fills count="6">
@@ -536,6 +684,12 @@
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F3F3"/>
+        <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -551,18 +705,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3F3F3"/>
-        <bgColor rgb="FFF3F3F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border/>
     <border>
       <left/>
@@ -575,11 +723,6 @@
       <bottom/>
     </border>
     <border>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <right/>
       <top/>
       <bottom/>
     </border>
@@ -639,78 +782,116 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <bottom/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="49">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="0" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="2" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="4" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="4" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="6" fillId="2" fontId="0" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="6" fillId="2" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -774,14 +955,14 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -933,7 +1114,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="2.88"/>
-    <col customWidth="1" min="2" max="2" width="56.25"/>
+    <col customWidth="1" min="2" max="2" width="58.0"/>
     <col customWidth="1" min="3" max="3" width="2.63"/>
     <col customWidth="1" min="4" max="4" width="2.75"/>
     <col customWidth="1" min="5" max="5" width="18.88"/>
@@ -950,1746 +1131,3857 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" ht="15.0" customHeight="1">
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="E2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" ht="15.0" customHeight="1">
+      <c r="B3" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="E3" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+    </row>
+    <row r="4" ht="15.0" customHeight="1">
+      <c r="A4" s="18"/>
+      <c r="C4" s="16"/>
+      <c r="E4" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="15.0" customHeight="1">
+      <c r="A5" s="18"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="E5" s="20" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" ht="15.0" customHeight="1">
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="E2" s="4" t="s">
+      <c r="F5" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="22"/>
+      <c r="H5" s="23"/>
+    </row>
+    <row r="6" ht="15.0" customHeight="1">
+      <c r="A6" s="18"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="25"/>
+    </row>
+    <row r="7" ht="15.0" customHeight="1">
+      <c r="A7" s="18"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="25"/>
+    </row>
+    <row r="8" ht="15.0" customHeight="1">
+      <c r="A8" s="18"/>
+      <c r="B8" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="25"/>
+    </row>
+    <row r="9" ht="15.0" customHeight="1">
+      <c r="A9" s="18"/>
+      <c r="B9" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="19">
+        <v>5.0</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="25"/>
+    </row>
+    <row r="10" ht="15.0" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="19">
+        <v>6.0</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="25"/>
+    </row>
+    <row r="11" ht="15.0" customHeight="1">
+      <c r="A11" s="18"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="19">
+        <v>7.0</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="25"/>
+    </row>
+    <row r="12" ht="15.0" customHeight="1">
+      <c r="A12" s="18"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="19">
+        <v>8.0</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="32"/>
+    </row>
+    <row r="13" ht="15.0" customHeight="1">
+      <c r="A13" s="18"/>
+      <c r="C13" s="16"/>
+    </row>
+    <row r="14" ht="30.0" customHeight="1">
+      <c r="A14" s="18"/>
+      <c r="C14" s="16"/>
+      <c r="E14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="K14" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+    </row>
+    <row r="15" ht="15.0" customHeight="1">
+      <c r="A15" s="18"/>
+      <c r="C15" s="16"/>
+      <c r="E15" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" ht="15.0" customHeight="1">
+      <c r="A16" s="18"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F16" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" ht="15.0" customHeight="1">
-      <c r="C3" s="7"/>
-      <c r="E3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="9"/>
-      <c r="C4" s="7"/>
-      <c r="E4" s="10" t="s">
+      <c r="G16" s="22"/>
+      <c r="H16" s="23"/>
+      <c r="J16" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="L16" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="M16" s="22"/>
+      <c r="N16" s="23"/>
+    </row>
+    <row r="17" ht="15.0" customHeight="1">
+      <c r="A17" s="18"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="F17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="G17" s="5"/>
+      <c r="H17" s="25"/>
+      <c r="J17" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M17" s="5"/>
+      <c r="N17" s="25"/>
+    </row>
+    <row r="18" ht="15.0" customHeight="1">
+      <c r="A18" s="18"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="E18" s="24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="9"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="10">
+      <c r="F18" s="3"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="25"/>
+      <c r="J18" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="25"/>
+    </row>
+    <row r="19" ht="15.0" customHeight="1">
+      <c r="A19" s="18"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="E19" s="24"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="25"/>
+      <c r="J19" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="K19" s="24"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="25"/>
+    </row>
+    <row r="20" ht="15.0" customHeight="1">
+      <c r="A20" s="18"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="19">
+        <v>5.0</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="19">
+        <v>5.0</v>
+      </c>
+      <c r="K20" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="M20" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="N20" s="34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="15.0" customHeight="1">
+      <c r="A21" s="18"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="19">
+        <v>6.0</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="19">
+        <v>6.0</v>
+      </c>
+      <c r="K21" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N21" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" ht="15.0" customHeight="1">
+      <c r="A22" s="18"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="19">
+        <v>7.0</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="19">
+        <v>7.0</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N22" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" ht="15.0" customHeight="1">
+      <c r="A23" s="18"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="19">
+        <v>8.0</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" s="19">
+        <v>8.0</v>
+      </c>
+      <c r="K23" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="L23" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="N23" s="32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="18"/>
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25" ht="44.25" customHeight="1">
+      <c r="A25" s="18"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="16"/>
+      <c r="E25" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+    </row>
+    <row r="26" ht="15.0" customHeight="1">
+      <c r="A26" s="18"/>
+      <c r="B26" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="E26" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+    </row>
+    <row r="27" ht="15.0" customHeight="1">
+      <c r="A27" s="18"/>
+      <c r="B27" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="E27" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" ht="15.0" customHeight="1">
+      <c r="A28" s="18"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="19">
         <v>1.0</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="12" t="s">
+      <c r="E28" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="G28" s="22"/>
+      <c r="H28" s="23"/>
+    </row>
+    <row r="29" ht="15.0" customHeight="1">
+      <c r="A29" s="18"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="5"/>
+      <c r="H29" s="25"/>
+    </row>
+    <row r="30" ht="15.0" customHeight="1">
+      <c r="A30" s="18"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="25"/>
+    </row>
+    <row r="31" ht="15.0" customHeight="1">
+      <c r="A31" s="18"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="E31" s="24"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="25"/>
+    </row>
+    <row r="32" ht="15.0" customHeight="1">
+      <c r="A32" s="18"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="19">
+        <v>5.0</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="12"/>
+      <c r="H32" s="34"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="C33" s="16"/>
+      <c r="D33" s="19">
+        <v>6.0</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" s="5"/>
+      <c r="H33" s="25"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="C34" s="16"/>
+      <c r="D34" s="19">
+        <v>7.0</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" s="5"/>
+      <c r="H34" s="25"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="B35" s="35"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="19">
+        <v>8.0</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="31"/>
+      <c r="H35" s="32"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="B36" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="16"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="B37" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="16"/>
+      <c r="E37" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="C38" s="16"/>
+      <c r="E38" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="C39" s="16"/>
+      <c r="D39" s="19">
+        <v>1.0</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="22"/>
+      <c r="H39" s="23"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="C40" s="16"/>
+      <c r="D40" s="19">
+        <v>2.0</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G40" s="5"/>
+      <c r="H40" s="25"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="C41" s="16"/>
+      <c r="D41" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="25"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="C42" s="16"/>
+      <c r="D42" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="E42" s="24"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="25"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="C43" s="16"/>
+      <c r="D43" s="19">
+        <v>5.0</v>
+      </c>
+      <c r="E43" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43" s="34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="C44" s="16"/>
+      <c r="D44" s="19">
+        <v>6.0</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H44" s="25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="C45" s="16"/>
+      <c r="D45" s="19">
+        <v>7.0</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H45" s="25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="C46" s="16"/>
+      <c r="D46" s="19">
+        <v>8.0</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H46" s="25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="B47" s="26"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="19">
+        <v>9.0</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H47" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="B48" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="16"/>
+      <c r="D48" s="19">
+        <v>10.0</v>
+      </c>
+      <c r="E48" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="F48" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="G48" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="H48" s="32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="B49" s="28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="E50" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="E51" s="37" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="E52" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G52" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H52" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="D53" s="38">
+        <v>1.0</v>
+      </c>
+      <c r="E53" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="F53" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="G53" s="22"/>
+      <c r="H53" s="23"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="D54" s="38">
+        <v>2.0</v>
+      </c>
+      <c r="E54" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="G54" s="5"/>
+      <c r="H54" s="25"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="B55" s="28"/>
+      <c r="D55" s="38">
+        <v>3.0</v>
+      </c>
+      <c r="E55" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="25"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="B56" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" s="38">
+        <v>4.0</v>
+      </c>
+      <c r="E56" s="24"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="25"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="D57" s="38">
+        <v>5.0</v>
+      </c>
+      <c r="E57" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="10">
+      <c r="F57" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="G57" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="H57" s="34"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="D58" s="38">
+        <v>6.0</v>
+      </c>
+      <c r="E58" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F58" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="G58" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="H58" s="25"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="D59" s="38">
+        <v>7.0</v>
+      </c>
+      <c r="E59" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="F59" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="G59" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="H59" s="32"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="B60" s="26"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="B61" s="26"/>
+      <c r="E61" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="17"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="B62" s="26"/>
+      <c r="E62" s="37" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="B63" s="26"/>
+      <c r="E63" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G63" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H63" s="19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="B64" s="26"/>
+      <c r="D64" s="38">
+        <v>1.0</v>
+      </c>
+      <c r="E64" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="F64" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="G64" s="22"/>
+      <c r="H64" s="23"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="B65" s="26"/>
+      <c r="D65" s="38">
         <v>2.0</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="16" t="s">
+      <c r="E65" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="F65" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="G65" s="5"/>
+      <c r="H65" s="25"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="B66" s="26"/>
+      <c r="D66" s="38">
+        <v>3.0</v>
+      </c>
+      <c r="E66" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="F66" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="G66" s="5"/>
+      <c r="H66" s="25"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="B67" s="26"/>
+      <c r="D67" s="38">
+        <v>4.0</v>
+      </c>
+      <c r="E67" s="24"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="25"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="D68" s="38">
+        <v>5.0</v>
+      </c>
+      <c r="E68" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="G68" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-    </row>
-    <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="9"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="18"/>
-    </row>
-    <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="9"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
-    </row>
-    <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="9"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="10">
-        <v>5.0</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="18"/>
-    </row>
-    <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="9"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="10">
+      <c r="H68" s="34"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="D69" s="38">
         <v>6.0</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
-    </row>
-    <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="9"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="10">
+      <c r="E69" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G69" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" s="25"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="D70" s="38">
         <v>7.0</v>
       </c>
-      <c r="E11" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-    </row>
-    <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="9"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="10">
-        <v>8.0</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" s="23"/>
-    </row>
-    <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="9"/>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" ht="30.0" customHeight="1">
-      <c r="A14" s="9"/>
-      <c r="C14" s="7"/>
-      <c r="E14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="K14" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="9"/>
-      <c r="C15" s="7"/>
-      <c r="E15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="9"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="14"/>
-      <c r="J16" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="M16" s="13"/>
-      <c r="N16" s="14"/>
-    </row>
-    <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="17"/>
-      <c r="H17" s="18"/>
-      <c r="J17" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="M17" s="17"/>
-      <c r="N17" s="18"/>
-    </row>
-    <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="18"/>
-      <c r="J18" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="16"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="18"/>
-    </row>
-    <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="18"/>
-      <c r="J19" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="18"/>
-    </row>
-    <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="10">
-        <v>5.0</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="20" t="s">
+      <c r="E70" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="J20" s="10">
-        <v>5.0</v>
-      </c>
-      <c r="K20" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="L20" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="N20" s="25" t="s">
+      <c r="F70" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="G70" s="48" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="10">
-        <v>6.0</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="10">
-        <v>6.0</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="L21" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="M21" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="N21" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="10">
-        <v>7.0</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="10">
-        <v>7.0</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="L22" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="M22" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="N22" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="10">
-        <v>8.0</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H23" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" s="10">
-        <v>8.0</v>
-      </c>
-      <c r="K23" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="L23" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="M23" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="N23" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" ht="30.0" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="C24" s="7"/>
-    </row>
-    <row r="25" ht="44.25" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="C25" s="7"/>
-      <c r="E25" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="C26" s="7"/>
-      <c r="E26" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-    </row>
-    <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="C27" s="7"/>
-      <c r="E27" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28" s="13"/>
-      <c r="H28" s="14"/>
-    </row>
-    <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="9"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="17"/>
-      <c r="H29" s="18"/>
-    </row>
-    <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="9"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="18"/>
-    </row>
-    <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="9"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="18"/>
-    </row>
-    <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="9"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="10">
-        <v>5.0</v>
-      </c>
-      <c r="E32" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="20"/>
-      <c r="H32" s="25"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="C33" s="7"/>
-      <c r="D33" s="10">
-        <v>6.0</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="G33" s="17"/>
-      <c r="H33" s="18"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="C34" s="7"/>
-      <c r="D34" s="10">
-        <v>7.0</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="G34" s="17"/>
-      <c r="H34" s="18"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="C35" s="7"/>
-      <c r="D35" s="10">
-        <v>8.0</v>
-      </c>
-      <c r="E35" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="G35" s="22"/>
-      <c r="H35" s="23"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="C36" s="7"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="C37" s="7"/>
-      <c r="E37" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="C38" s="7"/>
-      <c r="E38" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="C39" s="7"/>
-      <c r="D39" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G39" s="13"/>
-      <c r="H39" s="14"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="C40" s="7"/>
-      <c r="D40" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G40" s="17"/>
-      <c r="H40" s="18"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="C41" s="7"/>
-      <c r="D41" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F41" s="16"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="18"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="C42" s="7"/>
-      <c r="D42" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="18"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="C43" s="7"/>
-      <c r="D43" s="10">
-        <v>5.0</v>
-      </c>
-      <c r="E43" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H43" s="25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="C44" s="7"/>
-      <c r="D44" s="10">
-        <v>6.0</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H44" s="18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="B45" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="10">
-        <v>7.0</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F45" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G45" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="H45" s="18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="C46" s="7"/>
-      <c r="D46" s="10">
-        <v>8.0</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F46" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G46" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H46" s="18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="C47" s="7"/>
-      <c r="D47" s="10">
-        <v>9.0</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G47" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="H47" s="18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="C48" s="29"/>
-      <c r="D48" s="10">
-        <v>10.0</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="F48" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G48" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="H48" s="23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="B49" s="30"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
+      <c r="H70" s="32"/>
+    </row>
     <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="B72" s="26"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="B73" s="26"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="B74" s="26"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="B75" s="26"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="B76" s="26"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="B77" s="26"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="B78" s="26"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="B79" s="26"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="B80" s="26"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="B81" s="26"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="B82" s="26"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="B83" s="26"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="B84" s="26"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="B85" s="26"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="B86" s="26"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="B87" s="26"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="B88" s="26"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="B89" s="26"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="B90" s="26"/>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="B91" s="26"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="B92" s="26"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="B93" s="26"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="B94" s="26"/>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="B95" s="26"/>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="B96" s="26"/>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="B97" s="26"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="B98" s="26"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="B99" s="26"/>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="B100" s="26"/>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="B101" s="26"/>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="B102" s="26"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="B103" s="26"/>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="B104" s="26"/>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="B105" s="26"/>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="B106" s="26"/>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="B107" s="26"/>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="B108" s="26"/>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="B109" s="26"/>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="B110" s="26"/>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="B111" s="26"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="B112" s="26"/>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="B113" s="26"/>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="B114" s="26"/>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="B115" s="26"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="B116" s="26"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="B117" s="26"/>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="B118" s="26"/>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="B119" s="26"/>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="B120" s="26"/>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="B121" s="26"/>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="B122" s="26"/>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="B123" s="26"/>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="B124" s="26"/>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="B125" s="26"/>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="B126" s="26"/>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="B127" s="26"/>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="B128" s="26"/>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="B129" s="26"/>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="B130" s="26"/>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="B131" s="26"/>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="B132" s="26"/>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="B133" s="26"/>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="B134" s="26"/>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="B135" s="26"/>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="B136" s="26"/>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="B137" s="26"/>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="B138" s="26"/>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="B139" s="26"/>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="B140" s="26"/>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="B141" s="26"/>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="B142" s="26"/>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="B143" s="26"/>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="B144" s="26"/>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="B145" s="26"/>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="B146" s="26"/>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="B147" s="26"/>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="B148" s="26"/>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="B149" s="26"/>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="B150" s="26"/>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="B151" s="26"/>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="B152" s="26"/>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="B153" s="26"/>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="B154" s="26"/>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="B155" s="26"/>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="B156" s="26"/>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="B157" s="26"/>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="B158" s="26"/>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="B159" s="26"/>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="B160" s="26"/>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="B161" s="26"/>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="B162" s="26"/>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="B163" s="26"/>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="B164" s="26"/>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="B165" s="26"/>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="B166" s="26"/>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="B167" s="26"/>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="B168" s="26"/>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="B169" s="26"/>
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="B170" s="26"/>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="B171" s="26"/>
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="B172" s="26"/>
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="B173" s="26"/>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="B174" s="26"/>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="B175" s="26"/>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="B176" s="26"/>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="B177" s="26"/>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="B178" s="26"/>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="B179" s="26"/>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
+      <c r="B180" s="26"/>
+    </row>
+    <row r="181" ht="15.75" customHeight="1">
+      <c r="B181" s="26"/>
+    </row>
+    <row r="182" ht="15.75" customHeight="1">
+      <c r="B182" s="26"/>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="B183" s="26"/>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="B184" s="26"/>
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
+      <c r="B185" s="26"/>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="B186" s="26"/>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="B187" s="26"/>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
+      <c r="B188" s="26"/>
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
+      <c r="B189" s="26"/>
+    </row>
+    <row r="190" ht="15.75" customHeight="1">
+      <c r="B190" s="26"/>
+    </row>
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="B191" s="26"/>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="B192" s="26"/>
+    </row>
+    <row r="193" ht="15.75" customHeight="1">
+      <c r="B193" s="26"/>
+    </row>
+    <row r="194" ht="15.75" customHeight="1">
+      <c r="B194" s="26"/>
+    </row>
+    <row r="195" ht="15.75" customHeight="1">
+      <c r="B195" s="26"/>
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="B196" s="26"/>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="B197" s="26"/>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="B198" s="26"/>
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
+      <c r="B199" s="26"/>
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
+      <c r="B200" s="26"/>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="B201" s="26"/>
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
+      <c r="B202" s="26"/>
+    </row>
+    <row r="203" ht="15.75" customHeight="1">
+      <c r="B203" s="26"/>
+    </row>
+    <row r="204" ht="15.75" customHeight="1">
+      <c r="B204" s="26"/>
+    </row>
+    <row r="205" ht="15.75" customHeight="1">
+      <c r="B205" s="26"/>
+    </row>
+    <row r="206" ht="15.75" customHeight="1">
+      <c r="B206" s="26"/>
+    </row>
+    <row r="207" ht="15.75" customHeight="1">
+      <c r="B207" s="26"/>
+    </row>
+    <row r="208" ht="15.75" customHeight="1">
+      <c r="B208" s="26"/>
+    </row>
+    <row r="209" ht="15.75" customHeight="1">
+      <c r="B209" s="26"/>
+    </row>
+    <row r="210" ht="15.75" customHeight="1">
+      <c r="B210" s="26"/>
+    </row>
+    <row r="211" ht="15.75" customHeight="1">
+      <c r="B211" s="26"/>
+    </row>
+    <row r="212" ht="15.75" customHeight="1">
+      <c r="B212" s="26"/>
+    </row>
+    <row r="213" ht="15.75" customHeight="1">
+      <c r="B213" s="26"/>
+    </row>
+    <row r="214" ht="15.75" customHeight="1">
+      <c r="B214" s="26"/>
+    </row>
+    <row r="215" ht="15.75" customHeight="1">
+      <c r="B215" s="26"/>
+    </row>
+    <row r="216" ht="15.75" customHeight="1">
+      <c r="B216" s="26"/>
+    </row>
+    <row r="217" ht="15.75" customHeight="1">
+      <c r="B217" s="26"/>
+    </row>
+    <row r="218" ht="15.75" customHeight="1">
+      <c r="B218" s="26"/>
+    </row>
+    <row r="219" ht="15.75" customHeight="1">
+      <c r="B219" s="26"/>
+    </row>
+    <row r="220" ht="15.75" customHeight="1">
+      <c r="B220" s="26"/>
+    </row>
+    <row r="221" ht="15.75" customHeight="1">
+      <c r="B221" s="26"/>
+    </row>
+    <row r="222" ht="15.75" customHeight="1">
+      <c r="B222" s="26"/>
+    </row>
+    <row r="223" ht="15.75" customHeight="1">
+      <c r="B223" s="26"/>
+    </row>
+    <row r="224" ht="15.75" customHeight="1">
+      <c r="B224" s="26"/>
+    </row>
+    <row r="225" ht="15.75" customHeight="1">
+      <c r="B225" s="26"/>
+    </row>
+    <row r="226" ht="15.75" customHeight="1">
+      <c r="B226" s="26"/>
+    </row>
+    <row r="227" ht="15.75" customHeight="1">
+      <c r="B227" s="26"/>
+    </row>
+    <row r="228" ht="15.75" customHeight="1">
+      <c r="B228" s="26"/>
+    </row>
+    <row r="229" ht="15.75" customHeight="1">
+      <c r="B229" s="26"/>
+    </row>
+    <row r="230" ht="15.75" customHeight="1">
+      <c r="B230" s="26"/>
+    </row>
+    <row r="231" ht="15.75" customHeight="1">
+      <c r="B231" s="26"/>
+    </row>
+    <row r="232" ht="15.75" customHeight="1">
+      <c r="B232" s="26"/>
+    </row>
+    <row r="233" ht="15.75" customHeight="1">
+      <c r="B233" s="26"/>
+    </row>
+    <row r="234" ht="15.75" customHeight="1">
+      <c r="B234" s="26"/>
+    </row>
+    <row r="235" ht="15.75" customHeight="1">
+      <c r="B235" s="26"/>
+    </row>
+    <row r="236" ht="15.75" customHeight="1">
+      <c r="B236" s="26"/>
+    </row>
+    <row r="237" ht="15.75" customHeight="1">
+      <c r="B237" s="26"/>
+    </row>
+    <row r="238" ht="15.75" customHeight="1">
+      <c r="B238" s="26"/>
+    </row>
+    <row r="239" ht="15.75" customHeight="1">
+      <c r="B239" s="26"/>
+    </row>
+    <row r="240" ht="15.75" customHeight="1">
+      <c r="B240" s="26"/>
+    </row>
+    <row r="241" ht="15.75" customHeight="1">
+      <c r="B241" s="26"/>
+    </row>
+    <row r="242" ht="15.75" customHeight="1">
+      <c r="B242" s="26"/>
+    </row>
+    <row r="243" ht="15.75" customHeight="1">
+      <c r="B243" s="26"/>
+    </row>
+    <row r="244" ht="15.75" customHeight="1">
+      <c r="B244" s="26"/>
+    </row>
+    <row r="245" ht="15.75" customHeight="1">
+      <c r="B245" s="26"/>
+    </row>
+    <row r="246" ht="15.75" customHeight="1">
+      <c r="B246" s="26"/>
+    </row>
+    <row r="247" ht="15.75" customHeight="1">
+      <c r="B247" s="26"/>
+    </row>
+    <row r="248" ht="15.75" customHeight="1">
+      <c r="B248" s="26"/>
+    </row>
+    <row r="249" ht="15.75" customHeight="1">
+      <c r="B249" s="26"/>
+    </row>
+    <row r="250" ht="15.75" customHeight="1">
+      <c r="B250" s="26"/>
+    </row>
+    <row r="251" ht="15.75" customHeight="1">
+      <c r="B251" s="26"/>
+    </row>
+    <row r="252" ht="15.75" customHeight="1">
+      <c r="B252" s="26"/>
+    </row>
+    <row r="253" ht="15.75" customHeight="1">
+      <c r="B253" s="26"/>
+    </row>
+    <row r="254" ht="15.75" customHeight="1">
+      <c r="B254" s="26"/>
+    </row>
+    <row r="255" ht="15.75" customHeight="1">
+      <c r="B255" s="26"/>
+    </row>
+    <row r="256" ht="15.75" customHeight="1">
+      <c r="B256" s="26"/>
+    </row>
+    <row r="257" ht="15.75" customHeight="1">
+      <c r="B257" s="26"/>
+    </row>
+    <row r="258" ht="15.75" customHeight="1">
+      <c r="B258" s="26"/>
+    </row>
+    <row r="259" ht="15.75" customHeight="1">
+      <c r="B259" s="26"/>
+    </row>
+    <row r="260" ht="15.75" customHeight="1">
+      <c r="B260" s="26"/>
+    </row>
+    <row r="261" ht="15.75" customHeight="1">
+      <c r="B261" s="26"/>
+    </row>
+    <row r="262" ht="15.75" customHeight="1">
+      <c r="B262" s="26"/>
+    </row>
+    <row r="263" ht="15.75" customHeight="1">
+      <c r="B263" s="26"/>
+    </row>
+    <row r="264" ht="15.75" customHeight="1">
+      <c r="B264" s="26"/>
+    </row>
+    <row r="265" ht="15.75" customHeight="1">
+      <c r="B265" s="26"/>
+    </row>
+    <row r="266" ht="15.75" customHeight="1">
+      <c r="B266" s="26"/>
+    </row>
+    <row r="267" ht="15.75" customHeight="1">
+      <c r="B267" s="26"/>
+    </row>
+    <row r="268" ht="15.75" customHeight="1">
+      <c r="B268" s="26"/>
+    </row>
+    <row r="269" ht="15.75" customHeight="1">
+      <c r="B269" s="26"/>
+    </row>
+    <row r="270" ht="15.75" customHeight="1">
+      <c r="B270" s="26"/>
+    </row>
+    <row r="271" ht="15.75" customHeight="1">
+      <c r="B271" s="26"/>
+    </row>
+    <row r="272" ht="15.75" customHeight="1">
+      <c r="B272" s="26"/>
+    </row>
+    <row r="273" ht="15.75" customHeight="1">
+      <c r="B273" s="26"/>
+    </row>
+    <row r="274" ht="15.75" customHeight="1">
+      <c r="B274" s="26"/>
+    </row>
+    <row r="275" ht="15.75" customHeight="1">
+      <c r="B275" s="26"/>
+    </row>
+    <row r="276" ht="15.75" customHeight="1">
+      <c r="B276" s="26"/>
+    </row>
+    <row r="277" ht="15.75" customHeight="1">
+      <c r="B277" s="26"/>
+    </row>
+    <row r="278" ht="15.75" customHeight="1">
+      <c r="B278" s="26"/>
+    </row>
+    <row r="279" ht="15.75" customHeight="1">
+      <c r="B279" s="26"/>
+    </row>
+    <row r="280" ht="15.75" customHeight="1">
+      <c r="B280" s="26"/>
+    </row>
+    <row r="281" ht="15.75" customHeight="1">
+      <c r="B281" s="26"/>
+    </row>
+    <row r="282" ht="15.75" customHeight="1">
+      <c r="B282" s="26"/>
+    </row>
+    <row r="283" ht="15.75" customHeight="1">
+      <c r="B283" s="26"/>
+    </row>
+    <row r="284" ht="15.75" customHeight="1">
+      <c r="B284" s="26"/>
+    </row>
+    <row r="285" ht="15.75" customHeight="1">
+      <c r="B285" s="26"/>
+    </row>
+    <row r="286" ht="15.75" customHeight="1">
+      <c r="B286" s="26"/>
+    </row>
+    <row r="287" ht="15.75" customHeight="1">
+      <c r="B287" s="26"/>
+    </row>
+    <row r="288" ht="15.75" customHeight="1">
+      <c r="B288" s="26"/>
+    </row>
+    <row r="289" ht="15.75" customHeight="1">
+      <c r="B289" s="26"/>
+    </row>
+    <row r="290" ht="15.75" customHeight="1">
+      <c r="B290" s="26"/>
+    </row>
+    <row r="291" ht="15.75" customHeight="1">
+      <c r="B291" s="26"/>
+    </row>
+    <row r="292" ht="15.75" customHeight="1">
+      <c r="B292" s="26"/>
+    </row>
+    <row r="293" ht="15.75" customHeight="1">
+      <c r="B293" s="26"/>
+    </row>
+    <row r="294" ht="15.75" customHeight="1">
+      <c r="B294" s="26"/>
+    </row>
+    <row r="295" ht="15.75" customHeight="1">
+      <c r="B295" s="26"/>
+    </row>
+    <row r="296" ht="15.75" customHeight="1">
+      <c r="B296" s="26"/>
+    </row>
+    <row r="297" ht="15.75" customHeight="1">
+      <c r="B297" s="26"/>
+    </row>
+    <row r="298" ht="15.75" customHeight="1">
+      <c r="B298" s="26"/>
+    </row>
+    <row r="299" ht="15.75" customHeight="1">
+      <c r="B299" s="26"/>
+    </row>
+    <row r="300" ht="15.75" customHeight="1">
+      <c r="B300" s="26"/>
+    </row>
+    <row r="301" ht="15.75" customHeight="1">
+      <c r="B301" s="26"/>
+    </row>
+    <row r="302" ht="15.75" customHeight="1">
+      <c r="B302" s="26"/>
+    </row>
+    <row r="303" ht="15.75" customHeight="1">
+      <c r="B303" s="26"/>
+    </row>
+    <row r="304" ht="15.75" customHeight="1">
+      <c r="B304" s="26"/>
+    </row>
+    <row r="305" ht="15.75" customHeight="1">
+      <c r="B305" s="26"/>
+    </row>
+    <row r="306" ht="15.75" customHeight="1">
+      <c r="B306" s="26"/>
+    </row>
+    <row r="307" ht="15.75" customHeight="1">
+      <c r="B307" s="26"/>
+    </row>
+    <row r="308" ht="15.75" customHeight="1">
+      <c r="B308" s="26"/>
+    </row>
+    <row r="309" ht="15.75" customHeight="1">
+      <c r="B309" s="26"/>
+    </row>
+    <row r="310" ht="15.75" customHeight="1">
+      <c r="B310" s="26"/>
+    </row>
+    <row r="311" ht="15.75" customHeight="1">
+      <c r="B311" s="26"/>
+    </row>
+    <row r="312" ht="15.75" customHeight="1">
+      <c r="B312" s="26"/>
+    </row>
+    <row r="313" ht="15.75" customHeight="1">
+      <c r="B313" s="26"/>
+    </row>
+    <row r="314" ht="15.75" customHeight="1">
+      <c r="B314" s="26"/>
+    </row>
+    <row r="315" ht="15.75" customHeight="1">
+      <c r="B315" s="26"/>
+    </row>
+    <row r="316" ht="15.75" customHeight="1">
+      <c r="B316" s="26"/>
+    </row>
+    <row r="317" ht="15.75" customHeight="1">
+      <c r="B317" s="26"/>
+    </row>
+    <row r="318" ht="15.75" customHeight="1">
+      <c r="B318" s="26"/>
+    </row>
+    <row r="319" ht="15.75" customHeight="1">
+      <c r="B319" s="26"/>
+    </row>
+    <row r="320" ht="15.75" customHeight="1">
+      <c r="B320" s="26"/>
+    </row>
+    <row r="321" ht="15.75" customHeight="1">
+      <c r="B321" s="26"/>
+    </row>
+    <row r="322" ht="15.75" customHeight="1">
+      <c r="B322" s="26"/>
+    </row>
+    <row r="323" ht="15.75" customHeight="1">
+      <c r="B323" s="26"/>
+    </row>
+    <row r="324" ht="15.75" customHeight="1">
+      <c r="B324" s="26"/>
+    </row>
+    <row r="325" ht="15.75" customHeight="1">
+      <c r="B325" s="26"/>
+    </row>
+    <row r="326" ht="15.75" customHeight="1">
+      <c r="B326" s="26"/>
+    </row>
+    <row r="327" ht="15.75" customHeight="1">
+      <c r="B327" s="26"/>
+    </row>
+    <row r="328" ht="15.75" customHeight="1">
+      <c r="B328" s="26"/>
+    </row>
+    <row r="329" ht="15.75" customHeight="1">
+      <c r="B329" s="26"/>
+    </row>
+    <row r="330" ht="15.75" customHeight="1">
+      <c r="B330" s="26"/>
+    </row>
+    <row r="331" ht="15.75" customHeight="1">
+      <c r="B331" s="26"/>
+    </row>
+    <row r="332" ht="15.75" customHeight="1">
+      <c r="B332" s="26"/>
+    </row>
+    <row r="333" ht="15.75" customHeight="1">
+      <c r="B333" s="26"/>
+    </row>
+    <row r="334" ht="15.75" customHeight="1">
+      <c r="B334" s="26"/>
+    </row>
+    <row r="335" ht="15.75" customHeight="1">
+      <c r="B335" s="26"/>
+    </row>
+    <row r="336" ht="15.75" customHeight="1">
+      <c r="B336" s="26"/>
+    </row>
+    <row r="337" ht="15.75" customHeight="1">
+      <c r="B337" s="26"/>
+    </row>
+    <row r="338" ht="15.75" customHeight="1">
+      <c r="B338" s="26"/>
+    </row>
+    <row r="339" ht="15.75" customHeight="1">
+      <c r="B339" s="26"/>
+    </row>
+    <row r="340" ht="15.75" customHeight="1">
+      <c r="B340" s="26"/>
+    </row>
+    <row r="341" ht="15.75" customHeight="1">
+      <c r="B341" s="26"/>
+    </row>
+    <row r="342" ht="15.75" customHeight="1">
+      <c r="B342" s="26"/>
+    </row>
+    <row r="343" ht="15.75" customHeight="1">
+      <c r="B343" s="26"/>
+    </row>
+    <row r="344" ht="15.75" customHeight="1">
+      <c r="B344" s="26"/>
+    </row>
+    <row r="345" ht="15.75" customHeight="1">
+      <c r="B345" s="26"/>
+    </row>
+    <row r="346" ht="15.75" customHeight="1">
+      <c r="B346" s="26"/>
+    </row>
+    <row r="347" ht="15.75" customHeight="1">
+      <c r="B347" s="26"/>
+    </row>
+    <row r="348" ht="15.75" customHeight="1">
+      <c r="B348" s="26"/>
+    </row>
+    <row r="349" ht="15.75" customHeight="1">
+      <c r="B349" s="26"/>
+    </row>
+    <row r="350" ht="15.75" customHeight="1">
+      <c r="B350" s="26"/>
+    </row>
+    <row r="351" ht="15.75" customHeight="1">
+      <c r="B351" s="26"/>
+    </row>
+    <row r="352" ht="15.75" customHeight="1">
+      <c r="B352" s="26"/>
+    </row>
+    <row r="353" ht="15.75" customHeight="1">
+      <c r="B353" s="26"/>
+    </row>
+    <row r="354" ht="15.75" customHeight="1">
+      <c r="B354" s="26"/>
+    </row>
+    <row r="355" ht="15.75" customHeight="1">
+      <c r="B355" s="26"/>
+    </row>
+    <row r="356" ht="15.75" customHeight="1">
+      <c r="B356" s="26"/>
+    </row>
+    <row r="357" ht="15.75" customHeight="1">
+      <c r="B357" s="26"/>
+    </row>
+    <row r="358" ht="15.75" customHeight="1">
+      <c r="B358" s="26"/>
+    </row>
+    <row r="359" ht="15.75" customHeight="1">
+      <c r="B359" s="26"/>
+    </row>
+    <row r="360" ht="15.75" customHeight="1">
+      <c r="B360" s="26"/>
+    </row>
+    <row r="361" ht="15.75" customHeight="1">
+      <c r="B361" s="26"/>
+    </row>
+    <row r="362" ht="15.75" customHeight="1">
+      <c r="B362" s="26"/>
+    </row>
+    <row r="363" ht="15.75" customHeight="1">
+      <c r="B363" s="26"/>
+    </row>
+    <row r="364" ht="15.75" customHeight="1">
+      <c r="B364" s="26"/>
+    </row>
+    <row r="365" ht="15.75" customHeight="1">
+      <c r="B365" s="26"/>
+    </row>
+    <row r="366" ht="15.75" customHeight="1">
+      <c r="B366" s="26"/>
+    </row>
+    <row r="367" ht="15.75" customHeight="1">
+      <c r="B367" s="26"/>
+    </row>
+    <row r="368" ht="15.75" customHeight="1">
+      <c r="B368" s="26"/>
+    </row>
+    <row r="369" ht="15.75" customHeight="1">
+      <c r="B369" s="26"/>
+    </row>
+    <row r="370" ht="15.75" customHeight="1">
+      <c r="B370" s="26"/>
+    </row>
+    <row r="371" ht="15.75" customHeight="1">
+      <c r="B371" s="26"/>
+    </row>
+    <row r="372" ht="15.75" customHeight="1">
+      <c r="B372" s="26"/>
+    </row>
+    <row r="373" ht="15.75" customHeight="1">
+      <c r="B373" s="26"/>
+    </row>
+    <row r="374" ht="15.75" customHeight="1">
+      <c r="B374" s="26"/>
+    </row>
+    <row r="375" ht="15.75" customHeight="1">
+      <c r="B375" s="26"/>
+    </row>
+    <row r="376" ht="15.75" customHeight="1">
+      <c r="B376" s="26"/>
+    </row>
+    <row r="377" ht="15.75" customHeight="1">
+      <c r="B377" s="26"/>
+    </row>
+    <row r="378" ht="15.75" customHeight="1">
+      <c r="B378" s="26"/>
+    </row>
+    <row r="379" ht="15.75" customHeight="1">
+      <c r="B379" s="26"/>
+    </row>
+    <row r="380" ht="15.75" customHeight="1">
+      <c r="B380" s="26"/>
+    </row>
+    <row r="381" ht="15.75" customHeight="1">
+      <c r="B381" s="26"/>
+    </row>
+    <row r="382" ht="15.75" customHeight="1">
+      <c r="B382" s="26"/>
+    </row>
+    <row r="383" ht="15.75" customHeight="1">
+      <c r="B383" s="26"/>
+    </row>
+    <row r="384" ht="15.75" customHeight="1">
+      <c r="B384" s="26"/>
+    </row>
+    <row r="385" ht="15.75" customHeight="1">
+      <c r="B385" s="26"/>
+    </row>
+    <row r="386" ht="15.75" customHeight="1">
+      <c r="B386" s="26"/>
+    </row>
+    <row r="387" ht="15.75" customHeight="1">
+      <c r="B387" s="26"/>
+    </row>
+    <row r="388" ht="15.75" customHeight="1">
+      <c r="B388" s="26"/>
+    </row>
+    <row r="389" ht="15.75" customHeight="1">
+      <c r="B389" s="26"/>
+    </row>
+    <row r="390" ht="15.75" customHeight="1">
+      <c r="B390" s="26"/>
+    </row>
+    <row r="391" ht="15.75" customHeight="1">
+      <c r="B391" s="26"/>
+    </row>
+    <row r="392" ht="15.75" customHeight="1">
+      <c r="B392" s="26"/>
+    </row>
+    <row r="393" ht="15.75" customHeight="1">
+      <c r="B393" s="26"/>
+    </row>
+    <row r="394" ht="15.75" customHeight="1">
+      <c r="B394" s="26"/>
+    </row>
+    <row r="395" ht="15.75" customHeight="1">
+      <c r="B395" s="26"/>
+    </row>
+    <row r="396" ht="15.75" customHeight="1">
+      <c r="B396" s="26"/>
+    </row>
+    <row r="397" ht="15.75" customHeight="1">
+      <c r="B397" s="26"/>
+    </row>
+    <row r="398" ht="15.75" customHeight="1">
+      <c r="B398" s="26"/>
+    </row>
+    <row r="399" ht="15.75" customHeight="1">
+      <c r="B399" s="26"/>
+    </row>
+    <row r="400" ht="15.75" customHeight="1">
+      <c r="B400" s="26"/>
+    </row>
+    <row r="401" ht="15.75" customHeight="1">
+      <c r="B401" s="26"/>
+    </row>
+    <row r="402" ht="15.75" customHeight="1">
+      <c r="B402" s="26"/>
+    </row>
+    <row r="403" ht="15.75" customHeight="1">
+      <c r="B403" s="26"/>
+    </row>
+    <row r="404" ht="15.75" customHeight="1">
+      <c r="B404" s="26"/>
+    </row>
+    <row r="405" ht="15.75" customHeight="1">
+      <c r="B405" s="26"/>
+    </row>
+    <row r="406" ht="15.75" customHeight="1">
+      <c r="B406" s="26"/>
+    </row>
+    <row r="407" ht="15.75" customHeight="1">
+      <c r="B407" s="26"/>
+    </row>
+    <row r="408" ht="15.75" customHeight="1">
+      <c r="B408" s="26"/>
+    </row>
+    <row r="409" ht="15.75" customHeight="1">
+      <c r="B409" s="26"/>
+    </row>
+    <row r="410" ht="15.75" customHeight="1">
+      <c r="B410" s="26"/>
+    </row>
+    <row r="411" ht="15.75" customHeight="1">
+      <c r="B411" s="26"/>
+    </row>
+    <row r="412" ht="15.75" customHeight="1">
+      <c r="B412" s="26"/>
+    </row>
+    <row r="413" ht="15.75" customHeight="1">
+      <c r="B413" s="26"/>
+    </row>
+    <row r="414" ht="15.75" customHeight="1">
+      <c r="B414" s="26"/>
+    </row>
+    <row r="415" ht="15.75" customHeight="1">
+      <c r="B415" s="26"/>
+    </row>
+    <row r="416" ht="15.75" customHeight="1">
+      <c r="B416" s="26"/>
+    </row>
+    <row r="417" ht="15.75" customHeight="1">
+      <c r="B417" s="26"/>
+    </row>
+    <row r="418" ht="15.75" customHeight="1">
+      <c r="B418" s="26"/>
+    </row>
+    <row r="419" ht="15.75" customHeight="1">
+      <c r="B419" s="26"/>
+    </row>
+    <row r="420" ht="15.75" customHeight="1">
+      <c r="B420" s="26"/>
+    </row>
+    <row r="421" ht="15.75" customHeight="1">
+      <c r="B421" s="26"/>
+    </row>
+    <row r="422" ht="15.75" customHeight="1">
+      <c r="B422" s="26"/>
+    </row>
+    <row r="423" ht="15.75" customHeight="1">
+      <c r="B423" s="26"/>
+    </row>
+    <row r="424" ht="15.75" customHeight="1">
+      <c r="B424" s="26"/>
+    </row>
+    <row r="425" ht="15.75" customHeight="1">
+      <c r="B425" s="26"/>
+    </row>
+    <row r="426" ht="15.75" customHeight="1">
+      <c r="B426" s="26"/>
+    </row>
+    <row r="427" ht="15.75" customHeight="1">
+      <c r="B427" s="26"/>
+    </row>
+    <row r="428" ht="15.75" customHeight="1">
+      <c r="B428" s="26"/>
+    </row>
+    <row r="429" ht="15.75" customHeight="1">
+      <c r="B429" s="26"/>
+    </row>
+    <row r="430" ht="15.75" customHeight="1">
+      <c r="B430" s="26"/>
+    </row>
+    <row r="431" ht="15.75" customHeight="1">
+      <c r="B431" s="26"/>
+    </row>
+    <row r="432" ht="15.75" customHeight="1">
+      <c r="B432" s="26"/>
+    </row>
+    <row r="433" ht="15.75" customHeight="1">
+      <c r="B433" s="26"/>
+    </row>
+    <row r="434" ht="15.75" customHeight="1">
+      <c r="B434" s="26"/>
+    </row>
+    <row r="435" ht="15.75" customHeight="1">
+      <c r="B435" s="26"/>
+    </row>
+    <row r="436" ht="15.75" customHeight="1">
+      <c r="B436" s="26"/>
+    </row>
+    <row r="437" ht="15.75" customHeight="1">
+      <c r="B437" s="26"/>
+    </row>
+    <row r="438" ht="15.75" customHeight="1">
+      <c r="B438" s="26"/>
+    </row>
+    <row r="439" ht="15.75" customHeight="1">
+      <c r="B439" s="26"/>
+    </row>
+    <row r="440" ht="15.75" customHeight="1">
+      <c r="B440" s="26"/>
+    </row>
+    <row r="441" ht="15.75" customHeight="1">
+      <c r="B441" s="26"/>
+    </row>
+    <row r="442" ht="15.75" customHeight="1">
+      <c r="B442" s="26"/>
+    </row>
+    <row r="443" ht="15.75" customHeight="1">
+      <c r="B443" s="26"/>
+    </row>
+    <row r="444" ht="15.75" customHeight="1">
+      <c r="B444" s="26"/>
+    </row>
+    <row r="445" ht="15.75" customHeight="1">
+      <c r="B445" s="26"/>
+    </row>
+    <row r="446" ht="15.75" customHeight="1">
+      <c r="B446" s="26"/>
+    </row>
+    <row r="447" ht="15.75" customHeight="1">
+      <c r="B447" s="26"/>
+    </row>
+    <row r="448" ht="15.75" customHeight="1">
+      <c r="B448" s="26"/>
+    </row>
+    <row r="449" ht="15.75" customHeight="1">
+      <c r="B449" s="26"/>
+    </row>
+    <row r="450" ht="15.75" customHeight="1">
+      <c r="B450" s="26"/>
+    </row>
+    <row r="451" ht="15.75" customHeight="1">
+      <c r="B451" s="26"/>
+    </row>
+    <row r="452" ht="15.75" customHeight="1">
+      <c r="B452" s="26"/>
+    </row>
+    <row r="453" ht="15.75" customHeight="1">
+      <c r="B453" s="26"/>
+    </row>
+    <row r="454" ht="15.75" customHeight="1">
+      <c r="B454" s="26"/>
+    </row>
+    <row r="455" ht="15.75" customHeight="1">
+      <c r="B455" s="26"/>
+    </row>
+    <row r="456" ht="15.75" customHeight="1">
+      <c r="B456" s="26"/>
+    </row>
+    <row r="457" ht="15.75" customHeight="1">
+      <c r="B457" s="26"/>
+    </row>
+    <row r="458" ht="15.75" customHeight="1">
+      <c r="B458" s="26"/>
+    </row>
+    <row r="459" ht="15.75" customHeight="1">
+      <c r="B459" s="26"/>
+    </row>
+    <row r="460" ht="15.75" customHeight="1">
+      <c r="B460" s="26"/>
+    </row>
+    <row r="461" ht="15.75" customHeight="1">
+      <c r="B461" s="26"/>
+    </row>
+    <row r="462" ht="15.75" customHeight="1">
+      <c r="B462" s="26"/>
+    </row>
+    <row r="463" ht="15.75" customHeight="1">
+      <c r="B463" s="26"/>
+    </row>
+    <row r="464" ht="15.75" customHeight="1">
+      <c r="B464" s="26"/>
+    </row>
+    <row r="465" ht="15.75" customHeight="1">
+      <c r="B465" s="26"/>
+    </row>
+    <row r="466" ht="15.75" customHeight="1">
+      <c r="B466" s="26"/>
+    </row>
+    <row r="467" ht="15.75" customHeight="1">
+      <c r="B467" s="26"/>
+    </row>
+    <row r="468" ht="15.75" customHeight="1">
+      <c r="B468" s="26"/>
+    </row>
+    <row r="469" ht="15.75" customHeight="1">
+      <c r="B469" s="26"/>
+    </row>
+    <row r="470" ht="15.75" customHeight="1">
+      <c r="B470" s="26"/>
+    </row>
+    <row r="471" ht="15.75" customHeight="1">
+      <c r="B471" s="26"/>
+    </row>
+    <row r="472" ht="15.75" customHeight="1">
+      <c r="B472" s="26"/>
+    </row>
+    <row r="473" ht="15.75" customHeight="1">
+      <c r="B473" s="26"/>
+    </row>
+    <row r="474" ht="15.75" customHeight="1">
+      <c r="B474" s="26"/>
+    </row>
+    <row r="475" ht="15.75" customHeight="1">
+      <c r="B475" s="26"/>
+    </row>
+    <row r="476" ht="15.75" customHeight="1">
+      <c r="B476" s="26"/>
+    </row>
+    <row r="477" ht="15.75" customHeight="1">
+      <c r="B477" s="26"/>
+    </row>
+    <row r="478" ht="15.75" customHeight="1">
+      <c r="B478" s="26"/>
+    </row>
+    <row r="479" ht="15.75" customHeight="1">
+      <c r="B479" s="26"/>
+    </row>
+    <row r="480" ht="15.75" customHeight="1">
+      <c r="B480" s="26"/>
+    </row>
+    <row r="481" ht="15.75" customHeight="1">
+      <c r="B481" s="26"/>
+    </row>
+    <row r="482" ht="15.75" customHeight="1">
+      <c r="B482" s="26"/>
+    </row>
+    <row r="483" ht="15.75" customHeight="1">
+      <c r="B483" s="26"/>
+    </row>
+    <row r="484" ht="15.75" customHeight="1">
+      <c r="B484" s="26"/>
+    </row>
+    <row r="485" ht="15.75" customHeight="1">
+      <c r="B485" s="26"/>
+    </row>
+    <row r="486" ht="15.75" customHeight="1">
+      <c r="B486" s="26"/>
+    </row>
+    <row r="487" ht="15.75" customHeight="1">
+      <c r="B487" s="26"/>
+    </row>
+    <row r="488" ht="15.75" customHeight="1">
+      <c r="B488" s="26"/>
+    </row>
+    <row r="489" ht="15.75" customHeight="1">
+      <c r="B489" s="26"/>
+    </row>
+    <row r="490" ht="15.75" customHeight="1">
+      <c r="B490" s="26"/>
+    </row>
+    <row r="491" ht="15.75" customHeight="1">
+      <c r="B491" s="26"/>
+    </row>
+    <row r="492" ht="15.75" customHeight="1">
+      <c r="B492" s="26"/>
+    </row>
+    <row r="493" ht="15.75" customHeight="1">
+      <c r="B493" s="26"/>
+    </row>
+    <row r="494" ht="15.75" customHeight="1">
+      <c r="B494" s="26"/>
+    </row>
+    <row r="495" ht="15.75" customHeight="1">
+      <c r="B495" s="26"/>
+    </row>
+    <row r="496" ht="15.75" customHeight="1">
+      <c r="B496" s="26"/>
+    </row>
+    <row r="497" ht="15.75" customHeight="1">
+      <c r="B497" s="26"/>
+    </row>
+    <row r="498" ht="15.75" customHeight="1">
+      <c r="B498" s="26"/>
+    </row>
+    <row r="499" ht="15.75" customHeight="1">
+      <c r="B499" s="26"/>
+    </row>
+    <row r="500" ht="15.75" customHeight="1">
+      <c r="B500" s="26"/>
+    </row>
+    <row r="501" ht="15.75" customHeight="1">
+      <c r="B501" s="26"/>
+    </row>
+    <row r="502" ht="15.75" customHeight="1">
+      <c r="B502" s="26"/>
+    </row>
+    <row r="503" ht="15.75" customHeight="1">
+      <c r="B503" s="26"/>
+    </row>
+    <row r="504" ht="15.75" customHeight="1">
+      <c r="B504" s="26"/>
+    </row>
+    <row r="505" ht="15.75" customHeight="1">
+      <c r="B505" s="26"/>
+    </row>
+    <row r="506" ht="15.75" customHeight="1">
+      <c r="B506" s="26"/>
+    </row>
+    <row r="507" ht="15.75" customHeight="1">
+      <c r="B507" s="26"/>
+    </row>
+    <row r="508" ht="15.75" customHeight="1">
+      <c r="B508" s="26"/>
+    </row>
+    <row r="509" ht="15.75" customHeight="1">
+      <c r="B509" s="26"/>
+    </row>
+    <row r="510" ht="15.75" customHeight="1">
+      <c r="B510" s="26"/>
+    </row>
+    <row r="511" ht="15.75" customHeight="1">
+      <c r="B511" s="26"/>
+    </row>
+    <row r="512" ht="15.75" customHeight="1">
+      <c r="B512" s="26"/>
+    </row>
+    <row r="513" ht="15.75" customHeight="1">
+      <c r="B513" s="26"/>
+    </row>
+    <row r="514" ht="15.75" customHeight="1">
+      <c r="B514" s="26"/>
+    </row>
+    <row r="515" ht="15.75" customHeight="1">
+      <c r="B515" s="26"/>
+    </row>
+    <row r="516" ht="15.75" customHeight="1">
+      <c r="B516" s="26"/>
+    </row>
+    <row r="517" ht="15.75" customHeight="1">
+      <c r="B517" s="26"/>
+    </row>
+    <row r="518" ht="15.75" customHeight="1">
+      <c r="B518" s="26"/>
+    </row>
+    <row r="519" ht="15.75" customHeight="1">
+      <c r="B519" s="26"/>
+    </row>
+    <row r="520" ht="15.75" customHeight="1">
+      <c r="B520" s="26"/>
+    </row>
+    <row r="521" ht="15.75" customHeight="1">
+      <c r="B521" s="26"/>
+    </row>
+    <row r="522" ht="15.75" customHeight="1">
+      <c r="B522" s="26"/>
+    </row>
+    <row r="523" ht="15.75" customHeight="1">
+      <c r="B523" s="26"/>
+    </row>
+    <row r="524" ht="15.75" customHeight="1">
+      <c r="B524" s="26"/>
+    </row>
+    <row r="525" ht="15.75" customHeight="1">
+      <c r="B525" s="26"/>
+    </row>
+    <row r="526" ht="15.75" customHeight="1">
+      <c r="B526" s="26"/>
+    </row>
+    <row r="527" ht="15.75" customHeight="1">
+      <c r="B527" s="26"/>
+    </row>
+    <row r="528" ht="15.75" customHeight="1">
+      <c r="B528" s="26"/>
+    </row>
+    <row r="529" ht="15.75" customHeight="1">
+      <c r="B529" s="26"/>
+    </row>
+    <row r="530" ht="15.75" customHeight="1">
+      <c r="B530" s="26"/>
+    </row>
+    <row r="531" ht="15.75" customHeight="1">
+      <c r="B531" s="26"/>
+    </row>
+    <row r="532" ht="15.75" customHeight="1">
+      <c r="B532" s="26"/>
+    </row>
+    <row r="533" ht="15.75" customHeight="1">
+      <c r="B533" s="26"/>
+    </row>
+    <row r="534" ht="15.75" customHeight="1">
+      <c r="B534" s="26"/>
+    </row>
+    <row r="535" ht="15.75" customHeight="1">
+      <c r="B535" s="26"/>
+    </row>
+    <row r="536" ht="15.75" customHeight="1">
+      <c r="B536" s="26"/>
+    </row>
+    <row r="537" ht="15.75" customHeight="1">
+      <c r="B537" s="26"/>
+    </row>
+    <row r="538" ht="15.75" customHeight="1">
+      <c r="B538" s="26"/>
+    </row>
+    <row r="539" ht="15.75" customHeight="1">
+      <c r="B539" s="26"/>
+    </row>
+    <row r="540" ht="15.75" customHeight="1">
+      <c r="B540" s="26"/>
+    </row>
+    <row r="541" ht="15.75" customHeight="1">
+      <c r="B541" s="26"/>
+    </row>
+    <row r="542" ht="15.75" customHeight="1">
+      <c r="B542" s="26"/>
+    </row>
+    <row r="543" ht="15.75" customHeight="1">
+      <c r="B543" s="26"/>
+    </row>
+    <row r="544" ht="15.75" customHeight="1">
+      <c r="B544" s="26"/>
+    </row>
+    <row r="545" ht="15.75" customHeight="1">
+      <c r="B545" s="26"/>
+    </row>
+    <row r="546" ht="15.75" customHeight="1">
+      <c r="B546" s="26"/>
+    </row>
+    <row r="547" ht="15.75" customHeight="1">
+      <c r="B547" s="26"/>
+    </row>
+    <row r="548" ht="15.75" customHeight="1">
+      <c r="B548" s="26"/>
+    </row>
+    <row r="549" ht="15.75" customHeight="1">
+      <c r="B549" s="26"/>
+    </row>
+    <row r="550" ht="15.75" customHeight="1">
+      <c r="B550" s="26"/>
+    </row>
+    <row r="551" ht="15.75" customHeight="1">
+      <c r="B551" s="26"/>
+    </row>
+    <row r="552" ht="15.75" customHeight="1">
+      <c r="B552" s="26"/>
+    </row>
+    <row r="553" ht="15.75" customHeight="1">
+      <c r="B553" s="26"/>
+    </row>
+    <row r="554" ht="15.75" customHeight="1">
+      <c r="B554" s="26"/>
+    </row>
+    <row r="555" ht="15.75" customHeight="1">
+      <c r="B555" s="26"/>
+    </row>
+    <row r="556" ht="15.75" customHeight="1">
+      <c r="B556" s="26"/>
+    </row>
+    <row r="557" ht="15.75" customHeight="1">
+      <c r="B557" s="26"/>
+    </row>
+    <row r="558" ht="15.75" customHeight="1">
+      <c r="B558" s="26"/>
+    </row>
+    <row r="559" ht="15.75" customHeight="1">
+      <c r="B559" s="26"/>
+    </row>
+    <row r="560" ht="15.75" customHeight="1">
+      <c r="B560" s="26"/>
+    </row>
+    <row r="561" ht="15.75" customHeight="1">
+      <c r="B561" s="26"/>
+    </row>
+    <row r="562" ht="15.75" customHeight="1">
+      <c r="B562" s="26"/>
+    </row>
+    <row r="563" ht="15.75" customHeight="1">
+      <c r="B563" s="26"/>
+    </row>
+    <row r="564" ht="15.75" customHeight="1">
+      <c r="B564" s="26"/>
+    </row>
+    <row r="565" ht="15.75" customHeight="1">
+      <c r="B565" s="26"/>
+    </row>
+    <row r="566" ht="15.75" customHeight="1">
+      <c r="B566" s="26"/>
+    </row>
+    <row r="567" ht="15.75" customHeight="1">
+      <c r="B567" s="26"/>
+    </row>
+    <row r="568" ht="15.75" customHeight="1">
+      <c r="B568" s="26"/>
+    </row>
+    <row r="569" ht="15.75" customHeight="1">
+      <c r="B569" s="26"/>
+    </row>
+    <row r="570" ht="15.75" customHeight="1">
+      <c r="B570" s="26"/>
+    </row>
+    <row r="571" ht="15.75" customHeight="1">
+      <c r="B571" s="26"/>
+    </row>
+    <row r="572" ht="15.75" customHeight="1">
+      <c r="B572" s="26"/>
+    </row>
+    <row r="573" ht="15.75" customHeight="1">
+      <c r="B573" s="26"/>
+    </row>
+    <row r="574" ht="15.75" customHeight="1">
+      <c r="B574" s="26"/>
+    </row>
+    <row r="575" ht="15.75" customHeight="1">
+      <c r="B575" s="26"/>
+    </row>
+    <row r="576" ht="15.75" customHeight="1">
+      <c r="B576" s="26"/>
+    </row>
+    <row r="577" ht="15.75" customHeight="1">
+      <c r="B577" s="26"/>
+    </row>
+    <row r="578" ht="15.75" customHeight="1">
+      <c r="B578" s="26"/>
+    </row>
+    <row r="579" ht="15.75" customHeight="1">
+      <c r="B579" s="26"/>
+    </row>
+    <row r="580" ht="15.75" customHeight="1">
+      <c r="B580" s="26"/>
+    </row>
+    <row r="581" ht="15.75" customHeight="1">
+      <c r="B581" s="26"/>
+    </row>
+    <row r="582" ht="15.75" customHeight="1">
+      <c r="B582" s="26"/>
+    </row>
+    <row r="583" ht="15.75" customHeight="1">
+      <c r="B583" s="26"/>
+    </row>
+    <row r="584" ht="15.75" customHeight="1">
+      <c r="B584" s="26"/>
+    </row>
+    <row r="585" ht="15.75" customHeight="1">
+      <c r="B585" s="26"/>
+    </row>
+    <row r="586" ht="15.75" customHeight="1">
+      <c r="B586" s="26"/>
+    </row>
+    <row r="587" ht="15.75" customHeight="1">
+      <c r="B587" s="26"/>
+    </row>
+    <row r="588" ht="15.75" customHeight="1">
+      <c r="B588" s="26"/>
+    </row>
+    <row r="589" ht="15.75" customHeight="1">
+      <c r="B589" s="26"/>
+    </row>
+    <row r="590" ht="15.75" customHeight="1">
+      <c r="B590" s="26"/>
+    </row>
+    <row r="591" ht="15.75" customHeight="1">
+      <c r="B591" s="26"/>
+    </row>
+    <row r="592" ht="15.75" customHeight="1">
+      <c r="B592" s="26"/>
+    </row>
+    <row r="593" ht="15.75" customHeight="1">
+      <c r="B593" s="26"/>
+    </row>
+    <row r="594" ht="15.75" customHeight="1">
+      <c r="B594" s="26"/>
+    </row>
+    <row r="595" ht="15.75" customHeight="1">
+      <c r="B595" s="26"/>
+    </row>
+    <row r="596" ht="15.75" customHeight="1">
+      <c r="B596" s="26"/>
+    </row>
+    <row r="597" ht="15.75" customHeight="1">
+      <c r="B597" s="26"/>
+    </row>
+    <row r="598" ht="15.75" customHeight="1">
+      <c r="B598" s="26"/>
+    </row>
+    <row r="599" ht="15.75" customHeight="1">
+      <c r="B599" s="26"/>
+    </row>
+    <row r="600" ht="15.75" customHeight="1">
+      <c r="B600" s="26"/>
+    </row>
+    <row r="601" ht="15.75" customHeight="1">
+      <c r="B601" s="26"/>
+    </row>
+    <row r="602" ht="15.75" customHeight="1">
+      <c r="B602" s="26"/>
+    </row>
+    <row r="603" ht="15.75" customHeight="1">
+      <c r="B603" s="26"/>
+    </row>
+    <row r="604" ht="15.75" customHeight="1">
+      <c r="B604" s="26"/>
+    </row>
+    <row r="605" ht="15.75" customHeight="1">
+      <c r="B605" s="26"/>
+    </row>
+    <row r="606" ht="15.75" customHeight="1">
+      <c r="B606" s="26"/>
+    </row>
+    <row r="607" ht="15.75" customHeight="1">
+      <c r="B607" s="26"/>
+    </row>
+    <row r="608" ht="15.75" customHeight="1">
+      <c r="B608" s="26"/>
+    </row>
+    <row r="609" ht="15.75" customHeight="1">
+      <c r="B609" s="26"/>
+    </row>
+    <row r="610" ht="15.75" customHeight="1">
+      <c r="B610" s="26"/>
+    </row>
+    <row r="611" ht="15.75" customHeight="1">
+      <c r="B611" s="26"/>
+    </row>
+    <row r="612" ht="15.75" customHeight="1">
+      <c r="B612" s="26"/>
+    </row>
+    <row r="613" ht="15.75" customHeight="1">
+      <c r="B613" s="26"/>
+    </row>
+    <row r="614" ht="15.75" customHeight="1">
+      <c r="B614" s="26"/>
+    </row>
+    <row r="615" ht="15.75" customHeight="1">
+      <c r="B615" s="26"/>
+    </row>
+    <row r="616" ht="15.75" customHeight="1">
+      <c r="B616" s="26"/>
+    </row>
+    <row r="617" ht="15.75" customHeight="1">
+      <c r="B617" s="26"/>
+    </row>
+    <row r="618" ht="15.75" customHeight="1">
+      <c r="B618" s="26"/>
+    </row>
+    <row r="619" ht="15.75" customHeight="1">
+      <c r="B619" s="26"/>
+    </row>
+    <row r="620" ht="15.75" customHeight="1">
+      <c r="B620" s="26"/>
+    </row>
+    <row r="621" ht="15.75" customHeight="1">
+      <c r="B621" s="26"/>
+    </row>
+    <row r="622" ht="15.75" customHeight="1">
+      <c r="B622" s="26"/>
+    </row>
+    <row r="623" ht="15.75" customHeight="1">
+      <c r="B623" s="26"/>
+    </row>
+    <row r="624" ht="15.75" customHeight="1">
+      <c r="B624" s="26"/>
+    </row>
+    <row r="625" ht="15.75" customHeight="1">
+      <c r="B625" s="26"/>
+    </row>
+    <row r="626" ht="15.75" customHeight="1">
+      <c r="B626" s="26"/>
+    </row>
+    <row r="627" ht="15.75" customHeight="1">
+      <c r="B627" s="26"/>
+    </row>
+    <row r="628" ht="15.75" customHeight="1">
+      <c r="B628" s="26"/>
+    </row>
+    <row r="629" ht="15.75" customHeight="1">
+      <c r="B629" s="26"/>
+    </row>
+    <row r="630" ht="15.75" customHeight="1">
+      <c r="B630" s="26"/>
+    </row>
+    <row r="631" ht="15.75" customHeight="1">
+      <c r="B631" s="26"/>
+    </row>
+    <row r="632" ht="15.75" customHeight="1">
+      <c r="B632" s="26"/>
+    </row>
+    <row r="633" ht="15.75" customHeight="1">
+      <c r="B633" s="26"/>
+    </row>
+    <row r="634" ht="15.75" customHeight="1">
+      <c r="B634" s="26"/>
+    </row>
+    <row r="635" ht="15.75" customHeight="1">
+      <c r="B635" s="26"/>
+    </row>
+    <row r="636" ht="15.75" customHeight="1">
+      <c r="B636" s="26"/>
+    </row>
+    <row r="637" ht="15.75" customHeight="1">
+      <c r="B637" s="26"/>
+    </row>
+    <row r="638" ht="15.75" customHeight="1">
+      <c r="B638" s="26"/>
+    </row>
+    <row r="639" ht="15.75" customHeight="1">
+      <c r="B639" s="26"/>
+    </row>
+    <row r="640" ht="15.75" customHeight="1">
+      <c r="B640" s="26"/>
+    </row>
+    <row r="641" ht="15.75" customHeight="1">
+      <c r="B641" s="26"/>
+    </row>
+    <row r="642" ht="15.75" customHeight="1">
+      <c r="B642" s="26"/>
+    </row>
+    <row r="643" ht="15.75" customHeight="1">
+      <c r="B643" s="26"/>
+    </row>
+    <row r="644" ht="15.75" customHeight="1">
+      <c r="B644" s="26"/>
+    </row>
+    <row r="645" ht="15.75" customHeight="1">
+      <c r="B645" s="26"/>
+    </row>
+    <row r="646" ht="15.75" customHeight="1">
+      <c r="B646" s="26"/>
+    </row>
+    <row r="647" ht="15.75" customHeight="1">
+      <c r="B647" s="26"/>
+    </row>
+    <row r="648" ht="15.75" customHeight="1">
+      <c r="B648" s="26"/>
+    </row>
+    <row r="649" ht="15.75" customHeight="1">
+      <c r="B649" s="26"/>
+    </row>
+    <row r="650" ht="15.75" customHeight="1">
+      <c r="B650" s="26"/>
+    </row>
+    <row r="651" ht="15.75" customHeight="1">
+      <c r="B651" s="26"/>
+    </row>
+    <row r="652" ht="15.75" customHeight="1">
+      <c r="B652" s="26"/>
+    </row>
+    <row r="653" ht="15.75" customHeight="1">
+      <c r="B653" s="26"/>
+    </row>
+    <row r="654" ht="15.75" customHeight="1">
+      <c r="B654" s="26"/>
+    </row>
+    <row r="655" ht="15.75" customHeight="1">
+      <c r="B655" s="26"/>
+    </row>
+    <row r="656" ht="15.75" customHeight="1">
+      <c r="B656" s="26"/>
+    </row>
+    <row r="657" ht="15.75" customHeight="1">
+      <c r="B657" s="26"/>
+    </row>
+    <row r="658" ht="15.75" customHeight="1">
+      <c r="B658" s="26"/>
+    </row>
+    <row r="659" ht="15.75" customHeight="1">
+      <c r="B659" s="26"/>
+    </row>
+    <row r="660" ht="15.75" customHeight="1">
+      <c r="B660" s="26"/>
+    </row>
+    <row r="661" ht="15.75" customHeight="1">
+      <c r="B661" s="26"/>
+    </row>
+    <row r="662" ht="15.75" customHeight="1">
+      <c r="B662" s="26"/>
+    </row>
+    <row r="663" ht="15.75" customHeight="1">
+      <c r="B663" s="26"/>
+    </row>
+    <row r="664" ht="15.75" customHeight="1">
+      <c r="B664" s="26"/>
+    </row>
+    <row r="665" ht="15.75" customHeight="1">
+      <c r="B665" s="26"/>
+    </row>
+    <row r="666" ht="15.75" customHeight="1">
+      <c r="B666" s="26"/>
+    </row>
+    <row r="667" ht="15.75" customHeight="1">
+      <c r="B667" s="26"/>
+    </row>
+    <row r="668" ht="15.75" customHeight="1">
+      <c r="B668" s="26"/>
+    </row>
+    <row r="669" ht="15.75" customHeight="1">
+      <c r="B669" s="26"/>
+    </row>
+    <row r="670" ht="15.75" customHeight="1">
+      <c r="B670" s="26"/>
+    </row>
+    <row r="671" ht="15.75" customHeight="1">
+      <c r="B671" s="26"/>
+    </row>
+    <row r="672" ht="15.75" customHeight="1">
+      <c r="B672" s="26"/>
+    </row>
+    <row r="673" ht="15.75" customHeight="1">
+      <c r="B673" s="26"/>
+    </row>
+    <row r="674" ht="15.75" customHeight="1">
+      <c r="B674" s="26"/>
+    </row>
+    <row r="675" ht="15.75" customHeight="1">
+      <c r="B675" s="26"/>
+    </row>
+    <row r="676" ht="15.75" customHeight="1">
+      <c r="B676" s="26"/>
+    </row>
+    <row r="677" ht="15.75" customHeight="1">
+      <c r="B677" s="26"/>
+    </row>
+    <row r="678" ht="15.75" customHeight="1">
+      <c r="B678" s="26"/>
+    </row>
+    <row r="679" ht="15.75" customHeight="1">
+      <c r="B679" s="26"/>
+    </row>
+    <row r="680" ht="15.75" customHeight="1">
+      <c r="B680" s="26"/>
+    </row>
+    <row r="681" ht="15.75" customHeight="1">
+      <c r="B681" s="26"/>
+    </row>
+    <row r="682" ht="15.75" customHeight="1">
+      <c r="B682" s="26"/>
+    </row>
+    <row r="683" ht="15.75" customHeight="1">
+      <c r="B683" s="26"/>
+    </row>
+    <row r="684" ht="15.75" customHeight="1">
+      <c r="B684" s="26"/>
+    </row>
+    <row r="685" ht="15.75" customHeight="1">
+      <c r="B685" s="26"/>
+    </row>
+    <row r="686" ht="15.75" customHeight="1">
+      <c r="B686" s="26"/>
+    </row>
+    <row r="687" ht="15.75" customHeight="1">
+      <c r="B687" s="26"/>
+    </row>
+    <row r="688" ht="15.75" customHeight="1">
+      <c r="B688" s="26"/>
+    </row>
+    <row r="689" ht="15.75" customHeight="1">
+      <c r="B689" s="26"/>
+    </row>
+    <row r="690" ht="15.75" customHeight="1">
+      <c r="B690" s="26"/>
+    </row>
+    <row r="691" ht="15.75" customHeight="1">
+      <c r="B691" s="26"/>
+    </row>
+    <row r="692" ht="15.75" customHeight="1">
+      <c r="B692" s="26"/>
+    </row>
+    <row r="693" ht="15.75" customHeight="1">
+      <c r="B693" s="26"/>
+    </row>
+    <row r="694" ht="15.75" customHeight="1">
+      <c r="B694" s="26"/>
+    </row>
+    <row r="695" ht="15.75" customHeight="1">
+      <c r="B695" s="26"/>
+    </row>
+    <row r="696" ht="15.75" customHeight="1">
+      <c r="B696" s="26"/>
+    </row>
+    <row r="697" ht="15.75" customHeight="1">
+      <c r="B697" s="26"/>
+    </row>
+    <row r="698" ht="15.75" customHeight="1">
+      <c r="B698" s="26"/>
+    </row>
+    <row r="699" ht="15.75" customHeight="1">
+      <c r="B699" s="26"/>
+    </row>
+    <row r="700" ht="15.75" customHeight="1">
+      <c r="B700" s="26"/>
+    </row>
+    <row r="701" ht="15.75" customHeight="1">
+      <c r="B701" s="26"/>
+    </row>
+    <row r="702" ht="15.75" customHeight="1">
+      <c r="B702" s="26"/>
+    </row>
+    <row r="703" ht="15.75" customHeight="1">
+      <c r="B703" s="26"/>
+    </row>
+    <row r="704" ht="15.75" customHeight="1">
+      <c r="B704" s="26"/>
+    </row>
+    <row r="705" ht="15.75" customHeight="1">
+      <c r="B705" s="26"/>
+    </row>
+    <row r="706" ht="15.75" customHeight="1">
+      <c r="B706" s="26"/>
+    </row>
+    <row r="707" ht="15.75" customHeight="1">
+      <c r="B707" s="26"/>
+    </row>
+    <row r="708" ht="15.75" customHeight="1">
+      <c r="B708" s="26"/>
+    </row>
+    <row r="709" ht="15.75" customHeight="1">
+      <c r="B709" s="26"/>
+    </row>
+    <row r="710" ht="15.75" customHeight="1">
+      <c r="B710" s="26"/>
+    </row>
+    <row r="711" ht="15.75" customHeight="1">
+      <c r="B711" s="26"/>
+    </row>
+    <row r="712" ht="15.75" customHeight="1">
+      <c r="B712" s="26"/>
+    </row>
+    <row r="713" ht="15.75" customHeight="1">
+      <c r="B713" s="26"/>
+    </row>
+    <row r="714" ht="15.75" customHeight="1">
+      <c r="B714" s="26"/>
+    </row>
+    <row r="715" ht="15.75" customHeight="1">
+      <c r="B715" s="26"/>
+    </row>
+    <row r="716" ht="15.75" customHeight="1">
+      <c r="B716" s="26"/>
+    </row>
+    <row r="717" ht="15.75" customHeight="1">
+      <c r="B717" s="26"/>
+    </row>
+    <row r="718" ht="15.75" customHeight="1">
+      <c r="B718" s="26"/>
+    </row>
+    <row r="719" ht="15.75" customHeight="1">
+      <c r="B719" s="26"/>
+    </row>
+    <row r="720" ht="15.75" customHeight="1">
+      <c r="B720" s="26"/>
+    </row>
+    <row r="721" ht="15.75" customHeight="1">
+      <c r="B721" s="26"/>
+    </row>
+    <row r="722" ht="15.75" customHeight="1">
+      <c r="B722" s="26"/>
+    </row>
+    <row r="723" ht="15.75" customHeight="1">
+      <c r="B723" s="26"/>
+    </row>
+    <row r="724" ht="15.75" customHeight="1">
+      <c r="B724" s="26"/>
+    </row>
+    <row r="725" ht="15.75" customHeight="1">
+      <c r="B725" s="26"/>
+    </row>
+    <row r="726" ht="15.75" customHeight="1">
+      <c r="B726" s="26"/>
+    </row>
+    <row r="727" ht="15.75" customHeight="1">
+      <c r="B727" s="26"/>
+    </row>
+    <row r="728" ht="15.75" customHeight="1">
+      <c r="B728" s="26"/>
+    </row>
+    <row r="729" ht="15.75" customHeight="1">
+      <c r="B729" s="26"/>
+    </row>
+    <row r="730" ht="15.75" customHeight="1">
+      <c r="B730" s="26"/>
+    </row>
+    <row r="731" ht="15.75" customHeight="1">
+      <c r="B731" s="26"/>
+    </row>
+    <row r="732" ht="15.75" customHeight="1">
+      <c r="B732" s="26"/>
+    </row>
+    <row r="733" ht="15.75" customHeight="1">
+      <c r="B733" s="26"/>
+    </row>
+    <row r="734" ht="15.75" customHeight="1">
+      <c r="B734" s="26"/>
+    </row>
+    <row r="735" ht="15.75" customHeight="1">
+      <c r="B735" s="26"/>
+    </row>
+    <row r="736" ht="15.75" customHeight="1">
+      <c r="B736" s="26"/>
+    </row>
+    <row r="737" ht="15.75" customHeight="1">
+      <c r="B737" s="26"/>
+    </row>
+    <row r="738" ht="15.75" customHeight="1">
+      <c r="B738" s="26"/>
+    </row>
+    <row r="739" ht="15.75" customHeight="1">
+      <c r="B739" s="26"/>
+    </row>
+    <row r="740" ht="15.75" customHeight="1">
+      <c r="B740" s="26"/>
+    </row>
+    <row r="741" ht="15.75" customHeight="1">
+      <c r="B741" s="26"/>
+    </row>
+    <row r="742" ht="15.75" customHeight="1">
+      <c r="B742" s="26"/>
+    </row>
+    <row r="743" ht="15.75" customHeight="1">
+      <c r="B743" s="26"/>
+    </row>
+    <row r="744" ht="15.75" customHeight="1">
+      <c r="B744" s="26"/>
+    </row>
+    <row r="745" ht="15.75" customHeight="1">
+      <c r="B745" s="26"/>
+    </row>
+    <row r="746" ht="15.75" customHeight="1">
+      <c r="B746" s="26"/>
+    </row>
+    <row r="747" ht="15.75" customHeight="1">
+      <c r="B747" s="26"/>
+    </row>
+    <row r="748" ht="15.75" customHeight="1">
+      <c r="B748" s="26"/>
+    </row>
+    <row r="749" ht="15.75" customHeight="1">
+      <c r="B749" s="26"/>
+    </row>
+    <row r="750" ht="15.75" customHeight="1">
+      <c r="B750" s="26"/>
+    </row>
+    <row r="751" ht="15.75" customHeight="1">
+      <c r="B751" s="26"/>
+    </row>
+    <row r="752" ht="15.75" customHeight="1">
+      <c r="B752" s="26"/>
+    </row>
+    <row r="753" ht="15.75" customHeight="1">
+      <c r="B753" s="26"/>
+    </row>
+    <row r="754" ht="15.75" customHeight="1">
+      <c r="B754" s="26"/>
+    </row>
+    <row r="755" ht="15.75" customHeight="1">
+      <c r="B755" s="26"/>
+    </row>
+    <row r="756" ht="15.75" customHeight="1">
+      <c r="B756" s="26"/>
+    </row>
+    <row r="757" ht="15.75" customHeight="1">
+      <c r="B757" s="26"/>
+    </row>
+    <row r="758" ht="15.75" customHeight="1">
+      <c r="B758" s="26"/>
+    </row>
+    <row r="759" ht="15.75" customHeight="1">
+      <c r="B759" s="26"/>
+    </row>
+    <row r="760" ht="15.75" customHeight="1">
+      <c r="B760" s="26"/>
+    </row>
+    <row r="761" ht="15.75" customHeight="1">
+      <c r="B761" s="26"/>
+    </row>
+    <row r="762" ht="15.75" customHeight="1">
+      <c r="B762" s="26"/>
+    </row>
+    <row r="763" ht="15.75" customHeight="1">
+      <c r="B763" s="26"/>
+    </row>
+    <row r="764" ht="15.75" customHeight="1">
+      <c r="B764" s="26"/>
+    </row>
+    <row r="765" ht="15.75" customHeight="1">
+      <c r="B765" s="26"/>
+    </row>
+    <row r="766" ht="15.75" customHeight="1">
+      <c r="B766" s="26"/>
+    </row>
+    <row r="767" ht="15.75" customHeight="1">
+      <c r="B767" s="26"/>
+    </row>
+    <row r="768" ht="15.75" customHeight="1">
+      <c r="B768" s="26"/>
+    </row>
+    <row r="769" ht="15.75" customHeight="1">
+      <c r="B769" s="26"/>
+    </row>
+    <row r="770" ht="15.75" customHeight="1">
+      <c r="B770" s="26"/>
+    </row>
+    <row r="771" ht="15.75" customHeight="1">
+      <c r="B771" s="26"/>
+    </row>
+    <row r="772" ht="15.75" customHeight="1">
+      <c r="B772" s="26"/>
+    </row>
+    <row r="773" ht="15.75" customHeight="1">
+      <c r="B773" s="26"/>
+    </row>
+    <row r="774" ht="15.75" customHeight="1">
+      <c r="B774" s="26"/>
+    </row>
+    <row r="775" ht="15.75" customHeight="1">
+      <c r="B775" s="26"/>
+    </row>
+    <row r="776" ht="15.75" customHeight="1">
+      <c r="B776" s="26"/>
+    </row>
+    <row r="777" ht="15.75" customHeight="1">
+      <c r="B777" s="26"/>
+    </row>
+    <row r="778" ht="15.75" customHeight="1">
+      <c r="B778" s="26"/>
+    </row>
+    <row r="779" ht="15.75" customHeight="1">
+      <c r="B779" s="26"/>
+    </row>
+    <row r="780" ht="15.75" customHeight="1">
+      <c r="B780" s="26"/>
+    </row>
+    <row r="781" ht="15.75" customHeight="1">
+      <c r="B781" s="26"/>
+    </row>
+    <row r="782" ht="15.75" customHeight="1">
+      <c r="B782" s="26"/>
+    </row>
+    <row r="783" ht="15.75" customHeight="1">
+      <c r="B783" s="26"/>
+    </row>
+    <row r="784" ht="15.75" customHeight="1">
+      <c r="B784" s="26"/>
+    </row>
+    <row r="785" ht="15.75" customHeight="1">
+      <c r="B785" s="26"/>
+    </row>
+    <row r="786" ht="15.75" customHeight="1">
+      <c r="B786" s="26"/>
+    </row>
+    <row r="787" ht="15.75" customHeight="1">
+      <c r="B787" s="26"/>
+    </row>
+    <row r="788" ht="15.75" customHeight="1">
+      <c r="B788" s="26"/>
+    </row>
+    <row r="789" ht="15.75" customHeight="1">
+      <c r="B789" s="26"/>
+    </row>
+    <row r="790" ht="15.75" customHeight="1">
+      <c r="B790" s="26"/>
+    </row>
+    <row r="791" ht="15.75" customHeight="1">
+      <c r="B791" s="26"/>
+    </row>
+    <row r="792" ht="15.75" customHeight="1">
+      <c r="B792" s="26"/>
+    </row>
+    <row r="793" ht="15.75" customHeight="1">
+      <c r="B793" s="26"/>
+    </row>
+    <row r="794" ht="15.75" customHeight="1">
+      <c r="B794" s="26"/>
+    </row>
+    <row r="795" ht="15.75" customHeight="1">
+      <c r="B795" s="26"/>
+    </row>
+    <row r="796" ht="15.75" customHeight="1">
+      <c r="B796" s="26"/>
+    </row>
+    <row r="797" ht="15.75" customHeight="1">
+      <c r="B797" s="26"/>
+    </row>
+    <row r="798" ht="15.75" customHeight="1">
+      <c r="B798" s="26"/>
+    </row>
+    <row r="799" ht="15.75" customHeight="1">
+      <c r="B799" s="26"/>
+    </row>
+    <row r="800" ht="15.75" customHeight="1">
+      <c r="B800" s="26"/>
+    </row>
+    <row r="801" ht="15.75" customHeight="1">
+      <c r="B801" s="26"/>
+    </row>
+    <row r="802" ht="15.75" customHeight="1">
+      <c r="B802" s="26"/>
+    </row>
+    <row r="803" ht="15.75" customHeight="1">
+      <c r="B803" s="26"/>
+    </row>
+    <row r="804" ht="15.75" customHeight="1">
+      <c r="B804" s="26"/>
+    </row>
+    <row r="805" ht="15.75" customHeight="1">
+      <c r="B805" s="26"/>
+    </row>
+    <row r="806" ht="15.75" customHeight="1">
+      <c r="B806" s="26"/>
+    </row>
+    <row r="807" ht="15.75" customHeight="1">
+      <c r="B807" s="26"/>
+    </row>
+    <row r="808" ht="15.75" customHeight="1">
+      <c r="B808" s="26"/>
+    </row>
+    <row r="809" ht="15.75" customHeight="1">
+      <c r="B809" s="26"/>
+    </row>
+    <row r="810" ht="15.75" customHeight="1">
+      <c r="B810" s="26"/>
+    </row>
+    <row r="811" ht="15.75" customHeight="1">
+      <c r="B811" s="26"/>
+    </row>
+    <row r="812" ht="15.75" customHeight="1">
+      <c r="B812" s="26"/>
+    </row>
+    <row r="813" ht="15.75" customHeight="1">
+      <c r="B813" s="26"/>
+    </row>
+    <row r="814" ht="15.75" customHeight="1">
+      <c r="B814" s="26"/>
+    </row>
+    <row r="815" ht="15.75" customHeight="1">
+      <c r="B815" s="26"/>
+    </row>
+    <row r="816" ht="15.75" customHeight="1">
+      <c r="B816" s="26"/>
+    </row>
+    <row r="817" ht="15.75" customHeight="1">
+      <c r="B817" s="26"/>
+    </row>
+    <row r="818" ht="15.75" customHeight="1">
+      <c r="B818" s="26"/>
+    </row>
+    <row r="819" ht="15.75" customHeight="1">
+      <c r="B819" s="26"/>
+    </row>
+    <row r="820" ht="15.75" customHeight="1">
+      <c r="B820" s="26"/>
+    </row>
+    <row r="821" ht="15.75" customHeight="1">
+      <c r="B821" s="26"/>
+    </row>
+    <row r="822" ht="15.75" customHeight="1">
+      <c r="B822" s="26"/>
+    </row>
+    <row r="823" ht="15.75" customHeight="1">
+      <c r="B823" s="26"/>
+    </row>
+    <row r="824" ht="15.75" customHeight="1">
+      <c r="B824" s="26"/>
+    </row>
+    <row r="825" ht="15.75" customHeight="1">
+      <c r="B825" s="26"/>
+    </row>
+    <row r="826" ht="15.75" customHeight="1">
+      <c r="B826" s="26"/>
+    </row>
+    <row r="827" ht="15.75" customHeight="1">
+      <c r="B827" s="26"/>
+    </row>
+    <row r="828" ht="15.75" customHeight="1">
+      <c r="B828" s="26"/>
+    </row>
+    <row r="829" ht="15.75" customHeight="1">
+      <c r="B829" s="26"/>
+    </row>
+    <row r="830" ht="15.75" customHeight="1">
+      <c r="B830" s="26"/>
+    </row>
+    <row r="831" ht="15.75" customHeight="1">
+      <c r="B831" s="26"/>
+    </row>
+    <row r="832" ht="15.75" customHeight="1">
+      <c r="B832" s="26"/>
+    </row>
+    <row r="833" ht="15.75" customHeight="1">
+      <c r="B833" s="26"/>
+    </row>
+    <row r="834" ht="15.75" customHeight="1">
+      <c r="B834" s="26"/>
+    </row>
+    <row r="835" ht="15.75" customHeight="1">
+      <c r="B835" s="26"/>
+    </row>
+    <row r="836" ht="15.75" customHeight="1">
+      <c r="B836" s="26"/>
+    </row>
+    <row r="837" ht="15.75" customHeight="1">
+      <c r="B837" s="26"/>
+    </row>
+    <row r="838" ht="15.75" customHeight="1">
+      <c r="B838" s="26"/>
+    </row>
+    <row r="839" ht="15.75" customHeight="1">
+      <c r="B839" s="26"/>
+    </row>
+    <row r="840" ht="15.75" customHeight="1">
+      <c r="B840" s="26"/>
+    </row>
+    <row r="841" ht="15.75" customHeight="1">
+      <c r="B841" s="26"/>
+    </row>
+    <row r="842" ht="15.75" customHeight="1">
+      <c r="B842" s="26"/>
+    </row>
+    <row r="843" ht="15.75" customHeight="1">
+      <c r="B843" s="26"/>
+    </row>
+    <row r="844" ht="15.75" customHeight="1">
+      <c r="B844" s="26"/>
+    </row>
+    <row r="845" ht="15.75" customHeight="1">
+      <c r="B845" s="26"/>
+    </row>
+    <row r="846" ht="15.75" customHeight="1">
+      <c r="B846" s="26"/>
+    </row>
+    <row r="847" ht="15.75" customHeight="1">
+      <c r="B847" s="26"/>
+    </row>
+    <row r="848" ht="15.75" customHeight="1">
+      <c r="B848" s="26"/>
+    </row>
+    <row r="849" ht="15.75" customHeight="1">
+      <c r="B849" s="26"/>
+    </row>
+    <row r="850" ht="15.75" customHeight="1">
+      <c r="B850" s="26"/>
+    </row>
+    <row r="851" ht="15.75" customHeight="1">
+      <c r="B851" s="26"/>
+    </row>
+    <row r="852" ht="15.75" customHeight="1">
+      <c r="B852" s="26"/>
+    </row>
+    <row r="853" ht="15.75" customHeight="1">
+      <c r="B853" s="26"/>
+    </row>
+    <row r="854" ht="15.75" customHeight="1">
+      <c r="B854" s="26"/>
+    </row>
+    <row r="855" ht="15.75" customHeight="1">
+      <c r="B855" s="26"/>
+    </row>
+    <row r="856" ht="15.75" customHeight="1">
+      <c r="B856" s="26"/>
+    </row>
+    <row r="857" ht="15.75" customHeight="1">
+      <c r="B857" s="26"/>
+    </row>
+    <row r="858" ht="15.75" customHeight="1">
+      <c r="B858" s="26"/>
+    </row>
+    <row r="859" ht="15.75" customHeight="1">
+      <c r="B859" s="26"/>
+    </row>
+    <row r="860" ht="15.75" customHeight="1">
+      <c r="B860" s="26"/>
+    </row>
+    <row r="861" ht="15.75" customHeight="1">
+      <c r="B861" s="26"/>
+    </row>
+    <row r="862" ht="15.75" customHeight="1">
+      <c r="B862" s="26"/>
+    </row>
+    <row r="863" ht="15.75" customHeight="1">
+      <c r="B863" s="26"/>
+    </row>
+    <row r="864" ht="15.75" customHeight="1">
+      <c r="B864" s="26"/>
+    </row>
+    <row r="865" ht="15.75" customHeight="1">
+      <c r="B865" s="26"/>
+    </row>
+    <row r="866" ht="15.75" customHeight="1">
+      <c r="B866" s="26"/>
+    </row>
+    <row r="867" ht="15.75" customHeight="1">
+      <c r="B867" s="26"/>
+    </row>
+    <row r="868" ht="15.75" customHeight="1">
+      <c r="B868" s="26"/>
+    </row>
+    <row r="869" ht="15.75" customHeight="1">
+      <c r="B869" s="26"/>
+    </row>
+    <row r="870" ht="15.75" customHeight="1">
+      <c r="B870" s="26"/>
+    </row>
+    <row r="871" ht="15.75" customHeight="1">
+      <c r="B871" s="26"/>
+    </row>
+    <row r="872" ht="15.75" customHeight="1">
+      <c r="B872" s="26"/>
+    </row>
+    <row r="873" ht="15.75" customHeight="1">
+      <c r="B873" s="26"/>
+    </row>
+    <row r="874" ht="15.75" customHeight="1">
+      <c r="B874" s="26"/>
+    </row>
+    <row r="875" ht="15.75" customHeight="1">
+      <c r="B875" s="26"/>
+    </row>
+    <row r="876" ht="15.75" customHeight="1">
+      <c r="B876" s="26"/>
+    </row>
+    <row r="877" ht="15.75" customHeight="1">
+      <c r="B877" s="26"/>
+    </row>
+    <row r="878" ht="15.75" customHeight="1">
+      <c r="B878" s="26"/>
+    </row>
+    <row r="879" ht="15.75" customHeight="1">
+      <c r="B879" s="26"/>
+    </row>
+    <row r="880" ht="15.75" customHeight="1">
+      <c r="B880" s="26"/>
+    </row>
+    <row r="881" ht="15.75" customHeight="1">
+      <c r="B881" s="26"/>
+    </row>
+    <row r="882" ht="15.75" customHeight="1">
+      <c r="B882" s="26"/>
+    </row>
+    <row r="883" ht="15.75" customHeight="1">
+      <c r="B883" s="26"/>
+    </row>
+    <row r="884" ht="15.75" customHeight="1">
+      <c r="B884" s="26"/>
+    </row>
+    <row r="885" ht="15.75" customHeight="1">
+      <c r="B885" s="26"/>
+    </row>
+    <row r="886" ht="15.75" customHeight="1">
+      <c r="B886" s="26"/>
+    </row>
+    <row r="887" ht="15.75" customHeight="1">
+      <c r="B887" s="26"/>
+    </row>
+    <row r="888" ht="15.75" customHeight="1">
+      <c r="B888" s="26"/>
+    </row>
+    <row r="889" ht="15.75" customHeight="1">
+      <c r="B889" s="26"/>
+    </row>
+    <row r="890" ht="15.75" customHeight="1">
+      <c r="B890" s="26"/>
+    </row>
+    <row r="891" ht="15.75" customHeight="1">
+      <c r="B891" s="26"/>
+    </row>
+    <row r="892" ht="15.75" customHeight="1">
+      <c r="B892" s="26"/>
+    </row>
+    <row r="893" ht="15.75" customHeight="1">
+      <c r="B893" s="26"/>
+    </row>
+    <row r="894" ht="15.75" customHeight="1">
+      <c r="B894" s="26"/>
+    </row>
+    <row r="895" ht="15.75" customHeight="1">
+      <c r="B895" s="26"/>
+    </row>
+    <row r="896" ht="15.75" customHeight="1">
+      <c r="B896" s="26"/>
+    </row>
+    <row r="897" ht="15.75" customHeight="1">
+      <c r="B897" s="26"/>
+    </row>
+    <row r="898" ht="15.75" customHeight="1">
+      <c r="B898" s="26"/>
+    </row>
+    <row r="899" ht="15.75" customHeight="1">
+      <c r="B899" s="26"/>
+    </row>
+    <row r="900" ht="15.75" customHeight="1">
+      <c r="B900" s="26"/>
+    </row>
+    <row r="901" ht="15.75" customHeight="1">
+      <c r="B901" s="26"/>
+    </row>
+    <row r="902" ht="15.75" customHeight="1">
+      <c r="B902" s="26"/>
+    </row>
+    <row r="903" ht="15.75" customHeight="1">
+      <c r="B903" s="26"/>
+    </row>
+    <row r="904" ht="15.75" customHeight="1">
+      <c r="B904" s="26"/>
+    </row>
+    <row r="905" ht="15.75" customHeight="1">
+      <c r="B905" s="26"/>
+    </row>
+    <row r="906" ht="15.75" customHeight="1">
+      <c r="B906" s="26"/>
+    </row>
+    <row r="907" ht="15.75" customHeight="1">
+      <c r="B907" s="26"/>
+    </row>
+    <row r="908" ht="15.75" customHeight="1">
+      <c r="B908" s="26"/>
+    </row>
+    <row r="909" ht="15.75" customHeight="1">
+      <c r="B909" s="26"/>
+    </row>
+    <row r="910" ht="15.75" customHeight="1">
+      <c r="B910" s="26"/>
+    </row>
+    <row r="911" ht="15.75" customHeight="1">
+      <c r="B911" s="26"/>
+    </row>
+    <row r="912" ht="15.75" customHeight="1">
+      <c r="B912" s="26"/>
+    </row>
+    <row r="913" ht="15.75" customHeight="1">
+      <c r="B913" s="26"/>
+    </row>
+    <row r="914" ht="15.75" customHeight="1">
+      <c r="B914" s="26"/>
+    </row>
+    <row r="915" ht="15.75" customHeight="1">
+      <c r="B915" s="26"/>
+    </row>
+    <row r="916" ht="15.75" customHeight="1">
+      <c r="B916" s="26"/>
+    </row>
+    <row r="917" ht="15.75" customHeight="1">
+      <c r="B917" s="26"/>
+    </row>
+    <row r="918" ht="15.75" customHeight="1">
+      <c r="B918" s="26"/>
+    </row>
+    <row r="919" ht="15.75" customHeight="1">
+      <c r="B919" s="26"/>
+    </row>
+    <row r="920" ht="15.75" customHeight="1">
+      <c r="B920" s="26"/>
+    </row>
+    <row r="921" ht="15.75" customHeight="1">
+      <c r="B921" s="26"/>
+    </row>
+    <row r="922" ht="15.75" customHeight="1">
+      <c r="B922" s="26"/>
+    </row>
+    <row r="923" ht="15.75" customHeight="1">
+      <c r="B923" s="26"/>
+    </row>
+    <row r="924" ht="15.75" customHeight="1">
+      <c r="B924" s="26"/>
+    </row>
+    <row r="925" ht="15.75" customHeight="1">
+      <c r="B925" s="26"/>
+    </row>
+    <row r="926" ht="15.75" customHeight="1">
+      <c r="B926" s="26"/>
+    </row>
+    <row r="927" ht="15.75" customHeight="1">
+      <c r="B927" s="26"/>
+    </row>
+    <row r="928" ht="15.75" customHeight="1">
+      <c r="B928" s="26"/>
+    </row>
+    <row r="929" ht="15.75" customHeight="1">
+      <c r="B929" s="26"/>
+    </row>
+    <row r="930" ht="15.75" customHeight="1">
+      <c r="B930" s="26"/>
+    </row>
+    <row r="931" ht="15.75" customHeight="1">
+      <c r="B931" s="26"/>
+    </row>
+    <row r="932" ht="15.75" customHeight="1">
+      <c r="B932" s="26"/>
+    </row>
+    <row r="933" ht="15.75" customHeight="1">
+      <c r="B933" s="26"/>
+    </row>
+    <row r="934" ht="15.75" customHeight="1">
+      <c r="B934" s="26"/>
+    </row>
+    <row r="935" ht="15.75" customHeight="1">
+      <c r="B935" s="26"/>
+    </row>
+    <row r="936" ht="15.75" customHeight="1">
+      <c r="B936" s="26"/>
+    </row>
+    <row r="937" ht="15.75" customHeight="1">
+      <c r="B937" s="26"/>
+    </row>
+    <row r="938" ht="15.75" customHeight="1">
+      <c r="B938" s="26"/>
+    </row>
+    <row r="939" ht="15.75" customHeight="1">
+      <c r="B939" s="26"/>
+    </row>
+    <row r="940" ht="15.75" customHeight="1">
+      <c r="B940" s="26"/>
+    </row>
+    <row r="941" ht="15.75" customHeight="1">
+      <c r="B941" s="26"/>
+    </row>
+    <row r="942" ht="15.75" customHeight="1">
+      <c r="B942" s="26"/>
+    </row>
+    <row r="943" ht="15.75" customHeight="1">
+      <c r="B943" s="26"/>
+    </row>
+    <row r="944" ht="15.75" customHeight="1">
+      <c r="B944" s="26"/>
+    </row>
+    <row r="945" ht="15.75" customHeight="1">
+      <c r="B945" s="26"/>
+    </row>
+    <row r="946" ht="15.75" customHeight="1">
+      <c r="B946" s="26"/>
+    </row>
+    <row r="947" ht="15.75" customHeight="1">
+      <c r="B947" s="26"/>
+    </row>
+    <row r="948" ht="15.75" customHeight="1">
+      <c r="B948" s="26"/>
+    </row>
+    <row r="949" ht="15.75" customHeight="1">
+      <c r="B949" s="26"/>
+    </row>
+    <row r="950" ht="15.75" customHeight="1">
+      <c r="B950" s="26"/>
+    </row>
+    <row r="951" ht="15.75" customHeight="1">
+      <c r="B951" s="26"/>
+    </row>
+    <row r="952" ht="15.75" customHeight="1">
+      <c r="B952" s="26"/>
+    </row>
+    <row r="953" ht="15.75" customHeight="1">
+      <c r="B953" s="26"/>
+    </row>
+    <row r="954" ht="15.75" customHeight="1">
+      <c r="B954" s="26"/>
+    </row>
+    <row r="955" ht="15.75" customHeight="1">
+      <c r="B955" s="26"/>
+    </row>
+    <row r="956" ht="15.75" customHeight="1">
+      <c r="B956" s="26"/>
+    </row>
+    <row r="957" ht="15.75" customHeight="1">
+      <c r="B957" s="26"/>
+    </row>
+    <row r="958" ht="15.75" customHeight="1">
+      <c r="B958" s="26"/>
+    </row>
+    <row r="959" ht="15.75" customHeight="1">
+      <c r="B959" s="26"/>
+    </row>
+    <row r="960" ht="15.75" customHeight="1">
+      <c r="B960" s="26"/>
+    </row>
+    <row r="961" ht="15.75" customHeight="1">
+      <c r="B961" s="26"/>
+    </row>
+    <row r="962" ht="15.75" customHeight="1">
+      <c r="B962" s="26"/>
+    </row>
+    <row r="963" ht="15.75" customHeight="1">
+      <c r="B963" s="26"/>
+    </row>
+    <row r="964" ht="15.75" customHeight="1">
+      <c r="B964" s="26"/>
+    </row>
+    <row r="965" ht="15.75" customHeight="1">
+      <c r="B965" s="26"/>
+    </row>
+    <row r="966" ht="15.75" customHeight="1">
+      <c r="B966" s="26"/>
+    </row>
+    <row r="967" ht="15.75" customHeight="1">
+      <c r="B967" s="26"/>
+    </row>
+    <row r="968" ht="15.75" customHeight="1">
+      <c r="B968" s="26"/>
+    </row>
+    <row r="969" ht="15.75" customHeight="1">
+      <c r="B969" s="26"/>
+    </row>
+    <row r="970" ht="15.75" customHeight="1">
+      <c r="B970" s="26"/>
+    </row>
+    <row r="971" ht="15.75" customHeight="1">
+      <c r="B971" s="26"/>
+    </row>
+    <row r="972" ht="15.75" customHeight="1">
+      <c r="B972" s="26"/>
+    </row>
+    <row r="973" ht="15.75" customHeight="1">
+      <c r="B973" s="26"/>
+    </row>
+    <row r="974" ht="15.75" customHeight="1">
+      <c r="B974" s="26"/>
+    </row>
+    <row r="975" ht="15.75" customHeight="1">
+      <c r="B975" s="26"/>
+    </row>
+    <row r="976" ht="15.75" customHeight="1">
+      <c r="B976" s="26"/>
+    </row>
+    <row r="977" ht="15.75" customHeight="1">
+      <c r="B977" s="26"/>
+    </row>
+    <row r="978" ht="15.75" customHeight="1">
+      <c r="B978" s="26"/>
+    </row>
+    <row r="979" ht="15.75" customHeight="1">
+      <c r="B979" s="26"/>
+    </row>
+    <row r="980" ht="15.75" customHeight="1">
+      <c r="B980" s="26"/>
+    </row>
+    <row r="981" ht="15.75" customHeight="1">
+      <c r="B981" s="26"/>
+    </row>
+    <row r="982" ht="15.75" customHeight="1">
+      <c r="B982" s="26"/>
+    </row>
+    <row r="983" ht="15.75" customHeight="1">
+      <c r="B983" s="26"/>
+    </row>
+    <row r="984" ht="15.75" customHeight="1">
+      <c r="B984" s="26"/>
+    </row>
+    <row r="985" ht="15.75" customHeight="1">
+      <c r="B985" s="26"/>
+    </row>
+    <row r="986" ht="15.75" customHeight="1">
+      <c r="B986" s="26"/>
+    </row>
+    <row r="987" ht="15.75" customHeight="1">
+      <c r="B987" s="26"/>
+    </row>
+    <row r="988" ht="15.75" customHeight="1">
+      <c r="B988" s="26"/>
+    </row>
+    <row r="989" ht="15.75" customHeight="1">
+      <c r="B989" s="26"/>
+    </row>
+    <row r="990" ht="15.75" customHeight="1">
+      <c r="B990" s="26"/>
+    </row>
+    <row r="991" ht="15.75" customHeight="1">
+      <c r="B991" s="26"/>
+    </row>
+    <row r="992" ht="15.75" customHeight="1">
+      <c r="B992" s="26"/>
+    </row>
+    <row r="993" ht="15.75" customHeight="1">
+      <c r="B993" s="26"/>
+    </row>
+    <row r="994" ht="15.75" customHeight="1">
+      <c r="B994" s="26"/>
+    </row>
+    <row r="995" ht="15.75" customHeight="1">
+      <c r="B995" s="26"/>
+    </row>
+    <row r="996" ht="15.75" customHeight="1">
+      <c r="B996" s="26"/>
+    </row>
+    <row r="997" ht="15.75" customHeight="1">
+      <c r="B997" s="26"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="11">
+    <mergeCell ref="B9:B24"/>
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:B44"/>
     <mergeCell ref="C2:C48"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="K14:N14"/>
     <mergeCell ref="E25:H25"/>
-    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B37:B46"/>
+    <mergeCell ref="B27:B34"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="B56:B59"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId2" ref="B45"/>
+    <hyperlink r:id="rId2" ref="B56"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -2713,71 +5005,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="16" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="5"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4">
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="17"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="32" t="s">
+      <c r="B5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="17"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="17"/>
-    </row>
-    <row r="4">
-      <c r="C4" s="17"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="s">
+      <c r="C5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>15</v>
-      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="17"/>
+      <c r="A6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="17"/>
+      <c r="A7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3769,7 +6084,8 @@
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -3788,87 +6104,109 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="16" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4">
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="17"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="17"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="17"/>
-    </row>
-    <row r="4">
-      <c r="C4" s="17"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="17" t="s">
+      <c r="C7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>26</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -4860,6 +7198,7 @@
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>